--- a/outputs/robust_garch_order/garch_order_robustness_results.xlsx
+++ b/outputs/robust_garch_order/garch_order_robustness_results.xlsx
@@ -512,22 +512,22 @@
         <v>3123.19307180512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00201727022919965</v>
+        <v>0.00189112306407896</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0352633155653641</v>
+        <v>0.0334959739614401</v>
       </c>
       <c r="N2" t="n">
-        <v>-3049.56959468804</v>
+        <v>-3432.20987668332</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000902621772380509</v>
+        <v>0.000776474607259826</v>
       </c>
       <c r="P2" t="n">
-        <v>0.010988912913855</v>
+        <v>0.009221571309931</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6172.76266649316</v>
+        <v>-6555.40294848844</v>
       </c>
     </row>
     <row r="3">
@@ -565,22 +565,22 @@
         <v>3115.64269286866</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00196647553640656</v>
+        <v>0.00170428993353509</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0347985198843871</v>
+        <v>0.031638515430491</v>
       </c>
       <c r="N3" t="n">
-        <v>-3089.51991744256</v>
+        <v>-3814.1492762668</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000851391052111995</v>
+        <v>0.000589205449240522</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0105053283121689</v>
+        <v>0.00734532385827277</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6205.16261031122</v>
+        <v>-6929.79196913546</v>
       </c>
     </row>
     <row r="4">
@@ -618,22 +618,22 @@
         <v>3116.90594216604</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0148270242393051</v>
+        <v>0.0179798181829921</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0702594385008686</v>
+        <v>0.0756778006896337</v>
       </c>
       <c r="N4" t="n">
-        <v>-2306.58674429013</v>
+        <v>-2286.64384279436</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0137124642791035</v>
+        <v>0.0168652582227905</v>
       </c>
       <c r="P4" t="n">
-        <v>0.0459899035680408</v>
+        <v>0.0514082657568059</v>
       </c>
       <c r="Q4" t="n">
-        <v>-5423.49268645617</v>
+        <v>-5403.5497849604</v>
       </c>
     </row>
     <row r="5">
@@ -671,22 +671,22 @@
         <v>3009.76753253367</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00229487188617153</v>
+        <v>0.00230661634610298</v>
       </c>
       <c r="M5" t="n">
-        <v>0.035125334539763</v>
+        <v>0.036756273785361</v>
       </c>
       <c r="N5" t="n">
-        <v>-3059.47005380212</v>
+        <v>-2884.02345696939</v>
       </c>
       <c r="O5" t="n">
-        <v>0.00117962461936322</v>
+        <v>0.00119136907929468</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0108263432556263</v>
+        <v>0.0124572825012243</v>
       </c>
       <c r="Q5" t="n">
-        <v>-6069.23758633579</v>
+        <v>-5893.79098950306</v>
       </c>
     </row>
     <row r="6">
@@ -724,22 +724,22 @@
         <v>3119.15518848369</v>
       </c>
       <c r="L6" t="n">
-        <v>704873981129160553644680282668028684200202482428400820886068422626020842884400488</v>
+        <v>60964017116275469638042220628262848080622044046842224806264006888026026062</v>
       </c>
       <c r="M6" t="n">
-        <v>2805204585949946963040882462648842640422</v>
+        <v>981650919068874588244426280224428626</v>
       </c>
       <c r="N6" t="n">
-        <v>-2242.88022318053</v>
+        <v>-2243.74944963709</v>
       </c>
       <c r="O6" t="n">
-        <v>704873981129160553644680282668028684200202482428400820886068422626020842884400488</v>
+        <v>60964017116275469638042220628262848080622044046842224806264006888026026062</v>
       </c>
       <c r="P6" t="n">
-        <v>2805204585949946963040882462648842640422</v>
+        <v>981650919068874588244426280224428626</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5362.03541166422</v>
+        <v>-5362.90463812078</v>
       </c>
     </row>
     <row r="7">
@@ -777,22 +777,22 @@
         <v>3127.64203958365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00257433617073846</v>
+        <v>0.00220520186633019</v>
       </c>
       <c r="M7" t="n">
-        <v>0.038850383987985</v>
+        <v>0.0353889137531942</v>
       </c>
       <c r="N7" t="n">
-        <v>-2801.9019288023</v>
+        <v>-2995.78995311283</v>
       </c>
       <c r="O7" t="n">
-        <v>0.00145915859218697</v>
+        <v>0.0010900242877787</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0145538207176295</v>
+        <v>0.0110923504828387</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5929.54396838595</v>
+        <v>-6123.43199269648</v>
       </c>
     </row>
     <row r="8">
@@ -830,22 +830,22 @@
         <v>3988.11779242861</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000655947549806789</v>
+        <v>0.000603439498910087</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0196596403129826</v>
+        <v>0.0186983022570005</v>
       </c>
       <c r="N8" t="n">
-        <v>-3197.52677680734</v>
+        <v>-3434.88448559706</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000298806333521511</v>
+        <v>0.000246298282624808</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00636557842934739</v>
+        <v>0.00540424037336529</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7185.64456923595</v>
+        <v>-7423.00227802567</v>
       </c>
     </row>
     <row r="9">
@@ -883,22 +883,22 @@
         <v>3984.37601355569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00106508350993585</v>
+        <v>0.000718049142306875</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0248537222196043</v>
+        <v>0.0205267826929583</v>
       </c>
       <c r="N9" t="n">
-        <v>-2658.90319051843</v>
+        <v>-3045.22019278784</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000708008574375587</v>
+        <v>0.000360974206746608</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0115659172603578</v>
+        <v>0.00723897773371187</v>
       </c>
       <c r="Q9" t="n">
-        <v>-6643.27920407412</v>
+        <v>-7029.59620634353</v>
       </c>
     </row>
     <row r="10">
@@ -935,12 +935,24 @@
       <c r="K10" t="n">
         <v>4027.42598910073</v>
       </c>
-      <c r="L10"/>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10"/>
+      <c r="L10" t="n">
+        <v>0.000760462771378871</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0214402431002555</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-2846.80286414423</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.000403172713932192</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.00813565492841316</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>-6874.22885324496</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -976,12 +988,24 @@
       <c r="K11" t="n">
         <v>3890.62428993717</v>
       </c>
-      <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11"/>
+      <c r="L11" t="n">
+        <v>0.000629933513594605</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.0192188488529381</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-3124.59498648529</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.000272745919640342</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.00592123886547834</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-7015.21927642246</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1018,22 +1042,22 @@
         <v>3995.90239622051</v>
       </c>
       <c r="L12" t="n">
-        <v>0.00055268897701891</v>
+        <v>0.000618421395746589</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0178520460427794</v>
+        <v>0.01891999700827</v>
       </c>
       <c r="N12" t="n">
-        <v>-3593.75989351119</v>
+        <v>-3399.76416163086</v>
       </c>
       <c r="O12" t="n">
-        <v>0.000195437608719441</v>
+        <v>0.00026117002744712</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00454993688041374</v>
+        <v>0.00561788784590436</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7589.66228973171</v>
+        <v>-7395.66655785138</v>
       </c>
     </row>
     <row r="13">
@@ -1071,22 +1095,22 @@
         <v>3984.71555365199</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000575596254724273</v>
+        <v>0.000734639722147612</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0181836301973495</v>
+        <v>0.0206353288009437</v>
       </c>
       <c r="N13" t="n">
-        <v>-3445.30569880301</v>
+        <v>-3044.62841149482</v>
       </c>
       <c r="O13" t="n">
-        <v>0.000218466993390932</v>
+        <v>0.000377510460814271</v>
       </c>
       <c r="P13" t="n">
-        <v>0.00489054023884404</v>
+        <v>0.00734223884243832</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7430.021252455</v>
+        <v>-7029.34396514681</v>
       </c>
     </row>
     <row r="14">
@@ -1124,22 +1148,22 @@
         <v>3775.86640303834</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000501171774367368</v>
+        <v>0.000502152666109842</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0159304788612574</v>
+        <v>0.0159278626970238</v>
       </c>
       <c r="N14" t="n">
-        <v>-132866.023500218</v>
+        <v>-132530.162901</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0000034312626436201</v>
+        <v>0.00000441215438609372</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0000849920486354974</v>
+        <v>0.0000823758844019779</v>
       </c>
       <c r="Q14" t="n">
-        <v>-136641.889903256</v>
+        <v>-136306.029304038</v>
       </c>
     </row>
     <row r="15">
@@ -1177,22 +1201,22 @@
         <v>3770.36100626239</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0011266418938788</v>
+        <v>0.00117044704898243</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0261981622466156</v>
+        <v>0.0267486579531441</v>
       </c>
       <c r="N15" t="n">
-        <v>-2890.39366040447</v>
+        <v>-2880.70577376743</v>
       </c>
       <c r="O15" t="n">
-        <v>0.000628871827567963</v>
+        <v>0.00067267698267159</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0103526435959042</v>
+        <v>0.0109031393024326</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6660.75466666687</v>
+        <v>-6651.06678002983</v>
       </c>
     </row>
     <row r="16">
@@ -1229,12 +1253,24 @@
       <c r="K16" t="n">
         <v>3408.00015714302</v>
       </c>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16"/>
+      <c r="L16" t="n">
+        <v>0.00105920520602997</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.0221796122621299</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-2924.8039829289</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.000561809922211798</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.0063138165575046</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-6332.80414007192</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -1270,12 +1306,24 @@
       <c r="K17" t="n">
         <v>3755.12028192146</v>
       </c>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
+      <c r="L17" t="n">
+        <v>0.000951124282123845</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.0232831771947112</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-3121.82013078468</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.000453576359427199</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.00743693371734754</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>-6876.94041270614</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -1312,22 +1360,22 @@
         <v>3772.44626204037</v>
       </c>
       <c r="L18" t="n">
-        <v>349189155230160877024448484044688204468680628484088240622</v>
+        <v>7795229435967214767264800044280860426222688206660868822648286</v>
       </c>
       <c r="M18" t="n">
-        <v>2512580986337617161868480606</v>
+        <v>297943460740652066644886688404</v>
       </c>
       <c r="N18" t="n">
-        <v>-2244.7432287029</v>
+        <v>-2242.93609094909</v>
       </c>
       <c r="O18" t="n">
-        <v>349189155230160877024448484044688204468680628484088240622</v>
+        <v>7795229435967214767264800044280860426222688206660868822648286</v>
       </c>
       <c r="P18" t="n">
-        <v>2512580986337617161868480606</v>
+        <v>297943460740652066644886688404</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6017.18949074327</v>
+        <v>-6015.38235298946</v>
       </c>
     </row>
     <row r="19">
@@ -1365,22 +1413,22 @@
         <v>3655.22998537484</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00113693931490363</v>
+        <v>0.00138904460507529</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0261966180892686</v>
+        <v>0.0289254622226108</v>
       </c>
       <c r="N19" t="n">
-        <v>-2868.91348587995</v>
+        <v>-2686.07970148789</v>
       </c>
       <c r="O19" t="n">
-        <v>0.000639281047257854</v>
+        <v>0.000891386337429509</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0103509937584271</v>
+        <v>0.0130798378917693</v>
       </c>
       <c r="Q19" t="n">
-        <v>-6524.14347125478</v>
+        <v>-6341.30968686272</v>
       </c>
     </row>
     <row r="20">
@@ -1418,22 +1466,22 @@
         <v>6117.39575516507</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0000525375969109649</v>
+        <v>0.000065069727669505</v>
       </c>
       <c r="M20" t="n">
-        <v>0.00576543152424436</v>
+        <v>0.0064282837158837</v>
       </c>
       <c r="N20" t="n">
-        <v>-2878.36666859879</v>
+        <v>-2645.53744184449</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0000304504591313624</v>
+        <v>0.0000429825898899025</v>
       </c>
       <c r="P20" t="n">
-        <v>0.00226378441818177</v>
+        <v>0.00292663660982111</v>
       </c>
       <c r="Q20" t="n">
-        <v>-8995.76242376386</v>
+        <v>-8762.93319700956</v>
       </c>
     </row>
     <row r="21">
@@ -1471,22 +1519,22 @@
         <v>6043.9607137356</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0000517521204473704</v>
+        <v>0.0000772454405730656</v>
       </c>
       <c r="M21" t="n">
-        <v>0.00571847456806552</v>
+        <v>0.00701293764268925</v>
       </c>
       <c r="N21" t="n">
-        <v>-2893.27538333341</v>
+        <v>-2558.14592869462</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0000296696025376216</v>
+        <v>0.0000551629226633169</v>
       </c>
       <c r="P21" t="n">
-        <v>0.00221732629662663</v>
+        <v>0.00351178937125037</v>
       </c>
       <c r="Q21" t="n">
-        <v>-8937.23609706901</v>
+        <v>-8602.10664243022</v>
       </c>
     </row>
     <row r="22">
@@ -1524,22 +1572,22 @@
         <v>5981.44223636607</v>
       </c>
       <c r="L22" t="n">
-        <v>0.000106363002520015</v>
+        <v>0.000143101793294955</v>
       </c>
       <c r="M22" t="n">
-        <v>0.00767957639470598</v>
+        <v>0.00848291019543404</v>
       </c>
       <c r="N22" t="n">
-        <v>-2414.50417059554</v>
+        <v>-2394.89377372327</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0000842819865424916</v>
+        <v>0.000121020777317432</v>
       </c>
       <c r="P22" t="n">
-        <v>0.00417863804226696</v>
+        <v>0.00498197184299502</v>
       </c>
       <c r="Q22" t="n">
-        <v>-8395.9464069616</v>
+        <v>-8376.33601008934</v>
       </c>
     </row>
     <row r="23">
@@ -1577,22 +1625,22 @@
         <v>6153.91647861519</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0000639577255281862</v>
+        <v>0.0000842452821784805</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0062136205446606</v>
+        <v>0.0069136224505582</v>
       </c>
       <c r="N23" t="n">
-        <v>-2597.97693335413</v>
+        <v>-2532.67949586232</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0000418787273920469</v>
+        <v>0.0000621662840423412</v>
       </c>
       <c r="P23" t="n">
-        <v>0.00271300534463052</v>
+        <v>0.00341300725052812</v>
       </c>
       <c r="Q23" t="n">
-        <v>-8751.89341196932</v>
+        <v>-8686.5959744775</v>
       </c>
     </row>
     <row r="24">
@@ -1630,22 +1678,22 @@
         <v>6112.72531273013</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0000537543551852295</v>
+        <v>0.0000498226504150957</v>
       </c>
       <c r="M24" t="n">
-        <v>0.00579737042453465</v>
+        <v>0.00551257693137966</v>
       </c>
       <c r="N24" t="n">
-        <v>-2790.29086486744</v>
+        <v>-2872.5790563123</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0000316701777176362</v>
+        <v>0.0000277384729475025</v>
       </c>
       <c r="P24" t="n">
-        <v>0.00229602383477954</v>
+        <v>0.00201123034162454</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8903.01617759756</v>
+        <v>-8985.30436904242</v>
       </c>
     </row>
     <row r="25">
@@ -1683,22 +1731,22 @@
         <v>6063.57101232905</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0000540139212937698</v>
+        <v>0.0000499657356715661</v>
       </c>
       <c r="M25" t="n">
-        <v>0.00580870891636134</v>
+        <v>0.00552098611098661</v>
       </c>
       <c r="N25" t="n">
-        <v>-2782.99204758454</v>
+        <v>-2870.72136887532</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0000319326169610211</v>
+        <v>0.0000278844313388175</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00230772726475566</v>
+        <v>0.00202000445938093</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8846.56305991359</v>
+        <v>-8934.29238120436</v>
       </c>
     </row>
     <row r="26">
@@ -1736,22 +1784,22 @@
         <v>5850.6497879914</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0000961325031945991</v>
+        <v>0.0000781637648316354</v>
       </c>
       <c r="M26" t="n">
-        <v>0.00747880787339388</v>
+        <v>0.00683835566177272</v>
       </c>
       <c r="N26" t="n">
-        <v>-2623.4648001159</v>
+        <v>-2784.28944748241</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0000618109880092099</v>
+        <v>0.0000438422496462463</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00316691898793482</v>
+        <v>0.00252646677631366</v>
       </c>
       <c r="Q26" t="n">
-        <v>-8474.1145881073</v>
+        <v>-8634.93923547382</v>
       </c>
     </row>
     <row r="27">
@@ -1789,22 +1837,22 @@
         <v>5884.64928742832</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0000774470140387123</v>
+        <v>0.0000673950785189792</v>
       </c>
       <c r="M27" t="n">
-        <v>0.00677488815152758</v>
+        <v>0.00635552510354276</v>
       </c>
       <c r="N27" t="n">
-        <v>-2792.71636771139</v>
+        <v>-2959.68707774938</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0000431253291940727</v>
+        <v>0.0000330733936743396</v>
       </c>
       <c r="P27" t="n">
-        <v>0.00246322901734676</v>
+        <v>0.00204386596936194</v>
       </c>
       <c r="Q27" t="n">
-        <v>-8677.36565513971</v>
+        <v>-8844.33636517769</v>
       </c>
     </row>
     <row r="28">
@@ -1842,22 +1890,22 @@
         <v>5806.24216921478</v>
       </c>
       <c r="L28" t="n">
-        <v>0.00109654442291063</v>
+        <v>0.00642000555912582</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0197014579420517</v>
+        <v>0.0349581642965182</v>
       </c>
       <c r="N28" t="n">
-        <v>-2266.72657793048</v>
+        <v>-2246.5410342726</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0010622215747443</v>
+        <v>0.00638568271095949</v>
       </c>
       <c r="P28" t="n">
-        <v>0.0153885971314655</v>
+        <v>0.0306453034859321</v>
       </c>
       <c r="Q28" t="n">
-        <v>-8072.96874714526</v>
+        <v>-8052.78320348738</v>
       </c>
     </row>
     <row r="29">
@@ -1895,22 +1943,22 @@
         <v>5868.82638053184</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0000806674044345036</v>
+        <v>0.0000888943682344723</v>
       </c>
       <c r="M29" t="n">
-        <v>0.00703842297266026</v>
+        <v>0.00733768900987442</v>
       </c>
       <c r="N29" t="n">
-        <v>-2760.03034741222</v>
+        <v>-2772.40113534026</v>
       </c>
       <c r="O29" t="n">
-        <v>0.0000463443157351829</v>
+        <v>0.0000545712795351516</v>
       </c>
       <c r="P29" t="n">
-        <v>0.00272546858230331</v>
+        <v>0.00302473461951747</v>
       </c>
       <c r="Q29" t="n">
-        <v>-8628.85672794406</v>
+        <v>-8641.22751587209</v>
       </c>
     </row>
     <row r="30">
@@ -1948,22 +1996,22 @@
         <v>5849.22822585094</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0000765960745898656</v>
+        <v>0.0000782250800409225</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00670968600637775</v>
+        <v>0.00689043371006009</v>
       </c>
       <c r="N30" t="n">
-        <v>-2869.32052752747</v>
+        <v>-2907.3235062575</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0000422745610258498</v>
+        <v>0.0000439035664769067</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0023977908062971</v>
+        <v>0.00257853850997945</v>
       </c>
       <c r="Q30" t="n">
-        <v>-8718.54875337841</v>
+        <v>-8756.55173210844</v>
       </c>
     </row>
     <row r="31">
@@ -2001,22 +2049,22 @@
         <v>5884.56321600794</v>
       </c>
       <c r="L31" t="n">
-        <v>0.000066090479413393</v>
+        <v>0.0000674573302144841</v>
       </c>
       <c r="M31" t="n">
-        <v>0.00624292932800336</v>
+        <v>0.00638284297204189</v>
       </c>
       <c r="N31" t="n">
-        <v>-3076.79106198208</v>
+        <v>-3123.77813002188</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0000317686515416888</v>
+        <v>0.0000331355023427799</v>
       </c>
       <c r="P31" t="n">
-        <v>0.00193136726567107</v>
+        <v>0.0020712809097096</v>
       </c>
       <c r="Q31" t="n">
-        <v>-8961.35427799001</v>
+        <v>-9008.34134602982</v>
       </c>
     </row>
     <row r="32">
@@ -2054,22 +2102,22 @@
         <v>5029.22619018546</v>
       </c>
       <c r="L32" t="n">
-        <v>0.000218565538399644</v>
+        <v>0.000273985981923216</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0115568349542216</v>
+        <v>0.0124952920128037</v>
       </c>
       <c r="N32" t="n">
-        <v>-2882.46523023742</v>
+        <v>-2693.09208844813</v>
       </c>
       <c r="O32" t="n">
-        <v>0.000120613250896148</v>
+        <v>0.00017603369441972</v>
       </c>
       <c r="P32" t="n">
-        <v>0.00393616176654917</v>
+        <v>0.00487461882513123</v>
       </c>
       <c r="Q32" t="n">
-        <v>-7911.69142042288</v>
+        <v>-7722.31827863359</v>
       </c>
     </row>
     <row r="33">
@@ -2107,22 +2155,22 @@
         <v>5035.98410313405</v>
       </c>
       <c r="L33" t="n">
-        <v>0.000214422153747609</v>
+        <v>0.000265143859086788</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0114383221008907</v>
+        <v>0.0123071550817222</v>
       </c>
       <c r="N33" t="n">
-        <v>-2905.82739871968</v>
+        <v>-2716.17413736708</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000116470767784255</v>
+        <v>0.000167192473123433</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00381806779741511</v>
+        <v>0.00468690077824668</v>
       </c>
       <c r="Q33" t="n">
-        <v>-7941.81150185374</v>
+        <v>-7752.15824050114</v>
       </c>
     </row>
     <row r="34">
@@ -2159,12 +2207,24 @@
       <c r="K34" t="n">
         <v>5038.02723708611</v>
       </c>
-      <c r="L34"/>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34"/>
+      <c r="L34" t="n">
+        <v>0.685286494487181</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.652959449050991</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-2243.60964305586</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.685188483832547</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.645327324887514</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>-7281.63688014196</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
@@ -2200,12 +2260,24 @@
       <c r="K35" t="n">
         <v>5049.20315589203</v>
       </c>
-      <c r="L35"/>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35"/>
+      <c r="L35" t="n">
+        <v>0.00025053377475417</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.0121864872849144</v>
+      </c>
+      <c r="N35" t="n">
+        <v>-2762.57134811931</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.000152540516304714</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.00455680202944279</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>-7811.77450401134</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -2242,22 +2314,22 @@
         <v>5044.08121193212</v>
       </c>
       <c r="L36" t="n">
-        <v>0.000228708931142036</v>
+        <v>0.000220696923973193</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0118544666686046</v>
+        <v>0.0117718713452747</v>
       </c>
       <c r="N36" t="n">
-        <v>-2918.17589533616</v>
+        <v>-2947.08862469118</v>
       </c>
       <c r="O36" t="n">
-        <v>0.000130725997085363</v>
+        <v>0.00012271398991652</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00422638540081235</v>
+        <v>0.00414379007748238</v>
       </c>
       <c r="Q36" t="n">
-        <v>-7962.25710726827</v>
+        <v>-7991.16983662329</v>
       </c>
     </row>
     <row r="37">
@@ -2295,22 +2367,22 @@
         <v>5051.80195164274</v>
       </c>
       <c r="L37" t="n">
-        <v>0.000224531187756511</v>
+        <v>0.000218892417344628</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0117400615886784</v>
+        <v>0.0117190372909432</v>
       </c>
       <c r="N37" t="n">
-        <v>-2939.69464961121</v>
+        <v>-2956.84846002226</v>
       </c>
       <c r="O37" t="n">
-        <v>0.000126548913645309</v>
+        <v>0.000120910143233426</v>
       </c>
       <c r="P37" t="n">
-        <v>0.00411208966517043</v>
+        <v>0.00409106536743519</v>
       </c>
       <c r="Q37" t="n">
-        <v>-7991.49660125396</v>
+        <v>-8008.650411665</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/robust_garch_order/garch_order_robustness_results.xlsx
+++ b/outputs/robust_garch_order/garch_order_robustness_results.xlsx
@@ -512,22 +512,22 @@
         <v>3123.19307180512</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00189112306407896</v>
+        <v>0.00190202309250879</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0334959739614401</v>
+        <v>0.0336758039166346</v>
       </c>
       <c r="N2" t="n">
-        <v>-3432.20987668332</v>
+        <v>-3353.41529367087</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000776474607259826</v>
+        <v>0.000787374635689649</v>
       </c>
       <c r="P2" t="n">
-        <v>0.009221571309931</v>
+        <v>0.00940140126512556</v>
       </c>
       <c r="Q2" t="n">
-        <v>-6555.40294848844</v>
+        <v>-6476.60836547599</v>
       </c>
     </row>
     <row r="3">
@@ -565,22 +565,22 @@
         <v>3115.64269286866</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00170428993353509</v>
+        <v>0.00212346990156093</v>
       </c>
       <c r="M3" t="n">
-        <v>0.031638515430491</v>
+        <v>0.0358181174412756</v>
       </c>
       <c r="N3" t="n">
-        <v>-3814.1492762668</v>
+        <v>-3143.43581143348</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000589205449240522</v>
+        <v>0.00100838541726636</v>
       </c>
       <c r="P3" t="n">
-        <v>0.00734532385827277</v>
+        <v>0.0115249258690573</v>
       </c>
       <c r="Q3" t="n">
-        <v>-6929.79196913546</v>
+        <v>-6259.07850430214</v>
       </c>
     </row>
     <row r="4">
@@ -617,24 +617,12 @@
       <c r="K4" t="n">
         <v>3116.90594216604</v>
       </c>
-      <c r="L4" t="n">
-        <v>0.0179798181829921</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.0756778006896337</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-2286.64384279436</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.0168652582227905</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.0514082657568059</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-5403.5497849604</v>
-      </c>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+      <c r="O4"/>
+      <c r="P4"/>
+      <c r="Q4"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
@@ -670,24 +658,12 @@
       <c r="K5" t="n">
         <v>3009.76753253367</v>
       </c>
-      <c r="L5" t="n">
-        <v>0.00230661634610298</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.036756273785361</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-2884.02345696939</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.00119136907929468</v>
-      </c>
-      <c r="P5" t="n">
-        <v>0.0124572825012243</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>-5893.79098950306</v>
-      </c>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+      <c r="P5"/>
+      <c r="Q5"/>
     </row>
     <row r="6">
       <c r="A6" t="s">
@@ -724,22 +700,22 @@
         <v>3119.15518848369</v>
       </c>
       <c r="L6" t="n">
-        <v>60964017116275469638042220628262848080622044046842224806264006888026026062</v>
+        <v>73954604115547512896640024688666648082282648488228400840426688268468806862844</v>
       </c>
       <c r="M6" t="n">
-        <v>981650919068874588244426280224428626</v>
+        <v>33566430128841934454466242006024644062</v>
       </c>
       <c r="N6" t="n">
-        <v>-2243.74944963709</v>
+        <v>-2243.50953093144</v>
       </c>
       <c r="O6" t="n">
-        <v>60964017116275469638042220628262848080622044046842224806264006888026026062</v>
+        <v>73954604115547512896640024688666648082282648488228400840426688268468806862844</v>
       </c>
       <c r="P6" t="n">
-        <v>981650919068874588244426280224428626</v>
+        <v>33566430128841934454466242006024644062</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5362.90463812078</v>
+        <v>-5362.66471941514</v>
       </c>
     </row>
     <row r="7">
@@ -777,22 +753,22 @@
         <v>3127.64203958365</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00220520186633019</v>
+        <v>0.00192262907856386</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0353889137531942</v>
+        <v>0.0338906674335605</v>
       </c>
       <c r="N7" t="n">
-        <v>-2995.78995311283</v>
+        <v>-3251.28147427566</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0010900242877787</v>
+        <v>0.000807451500012366</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0110923504828387</v>
+        <v>0.009594104163205</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6123.43199269648</v>
+        <v>-6378.92351385932</v>
       </c>
     </row>
     <row r="8">
@@ -830,22 +806,22 @@
         <v>3988.11779242861</v>
       </c>
       <c r="L8" t="n">
-        <v>0.000603439498910087</v>
+        <v>0.000613491365006613</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0186983022570005</v>
+        <v>0.0190700402540253</v>
       </c>
       <c r="N8" t="n">
-        <v>-3434.88448559706</v>
+        <v>-3284.9245422719</v>
       </c>
       <c r="O8" t="n">
-        <v>0.000246298282624808</v>
+        <v>0.000256350148721334</v>
       </c>
       <c r="P8" t="n">
-        <v>0.00540424037336529</v>
+        <v>0.00577597837039016</v>
       </c>
       <c r="Q8" t="n">
-        <v>-7423.00227802567</v>
+        <v>-7273.04233470051</v>
       </c>
     </row>
     <row r="9">
@@ -883,22 +859,22 @@
         <v>3984.37601355569</v>
       </c>
       <c r="L9" t="n">
-        <v>0.000718049142306875</v>
+        <v>0.00078848325236476</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0205267826929583</v>
+        <v>0.021216328826141</v>
       </c>
       <c r="N9" t="n">
-        <v>-3045.22019278784</v>
+        <v>-2830.52981145011</v>
       </c>
       <c r="O9" t="n">
-        <v>0.000360974206746608</v>
+        <v>0.000431408316804493</v>
       </c>
       <c r="P9" t="n">
-        <v>0.00723897773371187</v>
+        <v>0.00792852386689459</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7029.59620634353</v>
+        <v>-6814.90582500581</v>
       </c>
     </row>
     <row r="10">
@@ -935,24 +911,12 @@
       <c r="K10" t="n">
         <v>4027.42598910073</v>
       </c>
-      <c r="L10" t="n">
-        <v>0.000760462771378871</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.0214402431002555</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-2846.80286414423</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.000403172713932192</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.00813565492841316</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-6874.22885324496</v>
-      </c>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+      <c r="P10"/>
+      <c r="Q10"/>
     </row>
     <row r="11">
       <c r="A11" t="s">
@@ -988,24 +952,12 @@
       <c r="K11" t="n">
         <v>3890.62428993717</v>
       </c>
-      <c r="L11" t="n">
-        <v>0.000629933513594605</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.0192188488529381</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-3124.59498648529</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.000272745919640342</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.00592123886547834</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-7015.21927642246</v>
-      </c>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+      <c r="P11"/>
+      <c r="Q11"/>
     </row>
     <row r="12">
       <c r="A12" t="s">
@@ -1042,22 +994,22 @@
         <v>3995.90239622051</v>
       </c>
       <c r="L12" t="n">
-        <v>0.000618421395746589</v>
+        <v>0.000641317267030788</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01891999700827</v>
+        <v>0.0191562064930081</v>
       </c>
       <c r="N12" t="n">
-        <v>-3399.76416163086</v>
+        <v>-3268.95846878058</v>
       </c>
       <c r="O12" t="n">
-        <v>0.00026117002744712</v>
+        <v>0.000284065898731319</v>
       </c>
       <c r="P12" t="n">
-        <v>0.00561788784590436</v>
+        <v>0.00585409733064239</v>
       </c>
       <c r="Q12" t="n">
-        <v>-7395.66655785138</v>
+        <v>-7264.86086500109</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1047,22 @@
         <v>3984.71555365199</v>
       </c>
       <c r="L13" t="n">
-        <v>0.000734639722147612</v>
+        <v>0.000776151654793395</v>
       </c>
       <c r="M13" t="n">
-        <v>0.0206353288009437</v>
+        <v>0.0212299672662033</v>
       </c>
       <c r="N13" t="n">
-        <v>-3044.62841149482</v>
+        <v>-2937.08796428805</v>
       </c>
       <c r="O13" t="n">
-        <v>0.000377510460814271</v>
+        <v>0.000419022393460054</v>
       </c>
       <c r="P13" t="n">
-        <v>0.00734223884243832</v>
+        <v>0.00793687730769791</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7029.34396514681</v>
+        <v>-6921.80351794004</v>
       </c>
     </row>
     <row r="14">
@@ -1148,22 +1100,22 @@
         <v>3775.86640303834</v>
       </c>
       <c r="L14" t="n">
-        <v>0.000502152666109842</v>
+        <v>0.0004998141245652</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0159278626970238</v>
+        <v>0.0159254468932027</v>
       </c>
       <c r="N14" t="n">
-        <v>-132530.162901</v>
+        <v>-131488.439699598</v>
       </c>
       <c r="O14" t="n">
-        <v>0.00000441215438609372</v>
+        <v>0.0000020736128414524</v>
       </c>
       <c r="P14" t="n">
-        <v>0.0000823758844019779</v>
+        <v>0.0000799600805808202</v>
       </c>
       <c r="Q14" t="n">
-        <v>-136306.029304038</v>
+        <v>-135264.306102636</v>
       </c>
     </row>
     <row r="15">
@@ -1201,22 +1153,22 @@
         <v>3770.36100626239</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00117044704898243</v>
+        <v>0.00109677471352657</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0267486579531441</v>
+        <v>0.0253004114502537</v>
       </c>
       <c r="N15" t="n">
-        <v>-2880.70577376743</v>
+        <v>-2868.01215754347</v>
       </c>
       <c r="O15" t="n">
-        <v>0.00067267698267159</v>
+        <v>0.000599004647215737</v>
       </c>
       <c r="P15" t="n">
-        <v>0.0109031393024326</v>
+        <v>0.00945489279954224</v>
       </c>
       <c r="Q15" t="n">
-        <v>-6651.06678002983</v>
+        <v>-6638.37316380586</v>
       </c>
     </row>
     <row r="16">
@@ -1360,22 +1312,22 @@
         <v>3772.44626204037</v>
       </c>
       <c r="L18" t="n">
-        <v>7795229435967214767264800044280860426222688206660868822648286</v>
+        <v>2780524339291910829066886220228280208886886644040002028468644208</v>
       </c>
       <c r="M18" t="n">
-        <v>297943460740652066644886688404</v>
+        <v>7283944369916652698884882642408</v>
       </c>
       <c r="N18" t="n">
-        <v>-2242.93609094909</v>
+        <v>-2243.35888050633</v>
       </c>
       <c r="O18" t="n">
-        <v>7795229435967214767264800044280860426222688206660868822648286</v>
+        <v>2780524339291910829066886220228280208886886644040002028468644208</v>
       </c>
       <c r="P18" t="n">
-        <v>297943460740652066644886688404</v>
+        <v>7283944369916652698884882642408</v>
       </c>
       <c r="Q18" t="n">
-        <v>-6015.38235298946</v>
+        <v>-6015.8051425467</v>
       </c>
     </row>
     <row r="19">
@@ -1413,22 +1365,22 @@
         <v>3655.22998537484</v>
       </c>
       <c r="L19" t="n">
-        <v>0.00138904460507529</v>
+        <v>0.00136712307669806</v>
       </c>
       <c r="M19" t="n">
-        <v>0.0289254622226108</v>
+        <v>0.0288430941535996</v>
       </c>
       <c r="N19" t="n">
-        <v>-2686.07970148789</v>
+        <v>-2759.78587448466</v>
       </c>
       <c r="O19" t="n">
-        <v>0.000891386337429509</v>
+        <v>0.000869464809052282</v>
       </c>
       <c r="P19" t="n">
-        <v>0.0130798378917693</v>
+        <v>0.0129974698227581</v>
       </c>
       <c r="Q19" t="n">
-        <v>-6341.30968686272</v>
+        <v>-6415.0158598595</v>
       </c>
     </row>
     <row r="20">
@@ -1466,22 +1418,22 @@
         <v>6117.39575516507</v>
       </c>
       <c r="L20" t="n">
-        <v>0.000065069727669505</v>
+        <v>0.0000684697136403873</v>
       </c>
       <c r="M20" t="n">
-        <v>0.0064282837158837</v>
+        <v>0.00663650383089111</v>
       </c>
       <c r="N20" t="n">
-        <v>-2645.53744184449</v>
+        <v>-2609.55504894228</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0000429825898899025</v>
+        <v>0.0000463825758607848</v>
       </c>
       <c r="P20" t="n">
-        <v>0.00292663660982111</v>
+        <v>0.00313485672482852</v>
       </c>
       <c r="Q20" t="n">
-        <v>-8762.93319700956</v>
+        <v>-8726.95080410734</v>
       </c>
     </row>
     <row r="21">
@@ -1519,22 +1471,22 @@
         <v>6043.9607137356</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0000772454405730656</v>
+        <v>0.0000864325152929873</v>
       </c>
       <c r="M21" t="n">
-        <v>0.00701293764268925</v>
+        <v>0.00739260999190352</v>
       </c>
       <c r="N21" t="n">
-        <v>-2558.14592869462</v>
+        <v>-2532.0885718045</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0000551629226633169</v>
+        <v>0.0000643499973832386</v>
       </c>
       <c r="P21" t="n">
-        <v>0.00351178937125037</v>
+        <v>0.00389146172046463</v>
       </c>
       <c r="Q21" t="n">
-        <v>-8602.10664243022</v>
+        <v>-8576.0492855401</v>
       </c>
     </row>
     <row r="22">
@@ -1571,24 +1523,12 @@
       <c r="K22" t="n">
         <v>5981.44223636607</v>
       </c>
-      <c r="L22" t="n">
-        <v>0.000143101793294955</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.00848291019543404</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-2394.89377372327</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.000121020777317432</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0.00498197184299502</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>-8376.33601008934</v>
-      </c>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+      <c r="P22"/>
+      <c r="Q22"/>
     </row>
     <row r="23">
       <c r="A23" t="s">
@@ -1624,24 +1564,12 @@
       <c r="K23" t="n">
         <v>6153.91647861519</v>
       </c>
-      <c r="L23" t="n">
-        <v>0.0000842452821784805</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.0069136224505582</v>
-      </c>
-      <c r="N23" t="n">
-        <v>-2532.67949586232</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.0000621662840423412</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0.00341300725052812</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>-8686.5959744775</v>
-      </c>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+      <c r="P23"/>
+      <c r="Q23"/>
     </row>
     <row r="24">
       <c r="A24" t="s">
@@ -1678,22 +1606,22 @@
         <v>6112.72531273013</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0000498226504150957</v>
+        <v>0.0000604371607791775</v>
       </c>
       <c r="M24" t="n">
-        <v>0.00551257693137966</v>
+        <v>0.00611768541025055</v>
       </c>
       <c r="N24" t="n">
-        <v>-2872.5790563123</v>
+        <v>-2702.75678222766</v>
       </c>
       <c r="O24" t="n">
-        <v>0.0000277384729475025</v>
+        <v>0.0000383529833115843</v>
       </c>
       <c r="P24" t="n">
-        <v>0.00201123034162454</v>
+        <v>0.00261633882049544</v>
       </c>
       <c r="Q24" t="n">
-        <v>-8985.30436904242</v>
+        <v>-8815.48209495779</v>
       </c>
     </row>
     <row r="25">
@@ -1731,22 +1659,22 @@
         <v>6063.57101232905</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0000499657356715661</v>
+        <v>0.0000644126701447323</v>
       </c>
       <c r="M25" t="n">
-        <v>0.00552098611098661</v>
+        <v>0.00631364585314944</v>
       </c>
       <c r="N25" t="n">
-        <v>-2870.72136887532</v>
+        <v>-2660.81703282341</v>
       </c>
       <c r="O25" t="n">
-        <v>0.0000278844313388175</v>
+        <v>0.0000423313658119837</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00202000445938093</v>
+        <v>0.00281266420154376</v>
       </c>
       <c r="Q25" t="n">
-        <v>-8934.29238120436</v>
+        <v>-8724.38804515245</v>
       </c>
     </row>
     <row r="26">
@@ -1784,22 +1712,22 @@
         <v>5850.6497879914</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0000781637648316354</v>
+        <v>0.0000792105359641043</v>
       </c>
       <c r="M26" t="n">
-        <v>0.00683835566177272</v>
+        <v>0.00679725210034686</v>
       </c>
       <c r="N26" t="n">
-        <v>-2784.28944748241</v>
+        <v>-2778.9253468018</v>
       </c>
       <c r="O26" t="n">
-        <v>0.0000438422496462463</v>
+        <v>0.0000448890207787151</v>
       </c>
       <c r="P26" t="n">
-        <v>0.00252646677631366</v>
+        <v>0.0024853632148878</v>
       </c>
       <c r="Q26" t="n">
-        <v>-8634.93923547382</v>
+        <v>-8629.5751347932</v>
       </c>
     </row>
     <row r="27">
@@ -1837,22 +1765,22 @@
         <v>5884.64928742832</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0000673950785189792</v>
+        <v>0.000067380779782448</v>
       </c>
       <c r="M27" t="n">
-        <v>0.00635552510354276</v>
+        <v>0.00634640020093867</v>
       </c>
       <c r="N27" t="n">
-        <v>-2959.68707774938</v>
+        <v>-3065.16045477383</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0000330733936743396</v>
+        <v>0.0000330590949378084</v>
       </c>
       <c r="P27" t="n">
-        <v>0.00204386596936194</v>
+        <v>0.00203474106675785</v>
       </c>
       <c r="Q27" t="n">
-        <v>-8844.33636517769</v>
+        <v>-8949.80974220215</v>
       </c>
     </row>
     <row r="28">
@@ -1889,24 +1817,12 @@
       <c r="K28" t="n">
         <v>5806.24216921478</v>
       </c>
-      <c r="L28" t="n">
-        <v>0.00642000555912582</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.0349581642965182</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-2246.5410342726</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0.00638568271095949</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0.0306453034859321</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-8052.78320348738</v>
-      </c>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+      <c r="P28"/>
+      <c r="Q28"/>
     </row>
     <row r="29">
       <c r="A29" t="s">
@@ -1942,24 +1858,12 @@
       <c r="K29" t="n">
         <v>5868.82638053184</v>
       </c>
-      <c r="L29" t="n">
-        <v>0.0000888943682344723</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0.00733768900987442</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-2772.40113534026</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.0000545712795351516</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0.00302473461951747</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>-8641.22751587209</v>
-      </c>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+      <c r="P29"/>
+      <c r="Q29"/>
     </row>
     <row r="30">
       <c r="A30" t="s">
@@ -1996,22 +1900,22 @@
         <v>5849.22822585094</v>
       </c>
       <c r="L30" t="n">
-        <v>0.0000782250800409225</v>
+        <v>0.0000815454702069571</v>
       </c>
       <c r="M30" t="n">
-        <v>0.00689043371006009</v>
+        <v>0.00697096949283593</v>
       </c>
       <c r="N30" t="n">
-        <v>-2907.3235062575</v>
+        <v>-2871.78512943571</v>
       </c>
       <c r="O30" t="n">
-        <v>0.0000439035664769067</v>
+        <v>0.0000472239566429413</v>
       </c>
       <c r="P30" t="n">
-        <v>0.00257853850997945</v>
+        <v>0.00265907429275529</v>
       </c>
       <c r="Q30" t="n">
-        <v>-8756.55173210844</v>
+        <v>-8721.01335528665</v>
       </c>
     </row>
     <row r="31">
@@ -2049,22 +1953,22 @@
         <v>5884.56321600794</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0000674573302144841</v>
+        <v>0.000069142799401713</v>
       </c>
       <c r="M31" t="n">
-        <v>0.00638284297204189</v>
+        <v>0.00642797830720931</v>
       </c>
       <c r="N31" t="n">
-        <v>-3123.77813002188</v>
+        <v>-3098.7258568091</v>
       </c>
       <c r="O31" t="n">
-        <v>0.0000331355023427799</v>
+        <v>0.0000348209715300089</v>
       </c>
       <c r="P31" t="n">
-        <v>0.0020712809097096</v>
+        <v>0.00211641624487703</v>
       </c>
       <c r="Q31" t="n">
-        <v>-9008.34134602982</v>
+        <v>-8983.28907281704</v>
       </c>
     </row>
     <row r="32">
@@ -2102,22 +2006,22 @@
         <v>5029.22619018546</v>
       </c>
       <c r="L32" t="n">
-        <v>0.000273985981923216</v>
+        <v>0.000217388689408545</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0124952920128037</v>
+        <v>0.0116034393963345</v>
       </c>
       <c r="N32" t="n">
-        <v>-2693.09208844813</v>
+        <v>-3002.34134634544</v>
       </c>
       <c r="O32" t="n">
-        <v>0.00017603369441972</v>
+        <v>0.000119436401905049</v>
       </c>
       <c r="P32" t="n">
-        <v>0.00487461882513123</v>
+        <v>0.00398276620866208</v>
       </c>
       <c r="Q32" t="n">
-        <v>-7722.31827863359</v>
+        <v>-8031.5675365309</v>
       </c>
     </row>
     <row r="33">
@@ -2155,22 +2059,22 @@
         <v>5035.98410313405</v>
       </c>
       <c r="L33" t="n">
-        <v>0.000265143859086788</v>
+        <v>0.000205037519290683</v>
       </c>
       <c r="M33" t="n">
-        <v>0.0123071550817222</v>
+        <v>0.0111674428327975</v>
       </c>
       <c r="N33" t="n">
-        <v>-2716.17413736708</v>
+        <v>-2965.20459282729</v>
       </c>
       <c r="O33" t="n">
-        <v>0.000167192473123433</v>
+        <v>0.000107086133327328</v>
       </c>
       <c r="P33" t="n">
-        <v>0.00468690077824668</v>
+        <v>0.00354718852932196</v>
       </c>
       <c r="Q33" t="n">
-        <v>-7752.15824050114</v>
+        <v>-8001.18869596134</v>
       </c>
     </row>
     <row r="34">
@@ -2207,24 +2111,12 @@
       <c r="K34" t="n">
         <v>5038.02723708611</v>
       </c>
-      <c r="L34" t="n">
-        <v>0.685286494487181</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0.652959449050991</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-2243.60964305586</v>
-      </c>
-      <c r="O34" t="n">
-        <v>0.685188483832547</v>
-      </c>
-      <c r="P34" t="n">
-        <v>0.645327324887514</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>-7281.63688014196</v>
-      </c>
+      <c r="L34"/>
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+      <c r="P34"/>
+      <c r="Q34"/>
     </row>
     <row r="35">
       <c r="A35" t="s">
@@ -2260,24 +2152,12 @@
       <c r="K35" t="n">
         <v>5049.20315589203</v>
       </c>
-      <c r="L35" t="n">
-        <v>0.00025053377475417</v>
-      </c>
-      <c r="M35" t="n">
-        <v>0.0121864872849144</v>
-      </c>
-      <c r="N35" t="n">
-        <v>-2762.57134811931</v>
-      </c>
-      <c r="O35" t="n">
-        <v>0.000152540516304714</v>
-      </c>
-      <c r="P35" t="n">
-        <v>0.00455680202944279</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>-7811.77450401134</v>
-      </c>
+      <c r="L35"/>
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+      <c r="P35"/>
+      <c r="Q35"/>
     </row>
     <row r="36">
       <c r="A36" t="s">
@@ -2314,22 +2194,22 @@
         <v>5044.08121193212</v>
       </c>
       <c r="L36" t="n">
-        <v>0.000220696923973193</v>
+        <v>0.000273135773302722</v>
       </c>
       <c r="M36" t="n">
-        <v>0.0117718713452747</v>
+        <v>0.0125787898977313</v>
       </c>
       <c r="N36" t="n">
-        <v>-2947.08862469118</v>
+        <v>-2728.49170102051</v>
       </c>
       <c r="O36" t="n">
-        <v>0.00012271398991652</v>
+        <v>0.000175152839246049</v>
       </c>
       <c r="P36" t="n">
-        <v>0.00414379007748238</v>
+        <v>0.00495070862993907</v>
       </c>
       <c r="Q36" t="n">
-        <v>-7991.16983662329</v>
+        <v>-7772.57291295263</v>
       </c>
     </row>
     <row r="37">
@@ -2367,22 +2247,22 @@
         <v>5051.80195164274</v>
       </c>
       <c r="L37" t="n">
-        <v>0.000218892417344628</v>
+        <v>0.000268271765220214</v>
       </c>
       <c r="M37" t="n">
-        <v>0.0117190372909432</v>
+        <v>0.0124670111471548</v>
       </c>
       <c r="N37" t="n">
-        <v>-2956.84846002226</v>
+        <v>-2742.41983761846</v>
       </c>
       <c r="O37" t="n">
-        <v>0.000120910143233426</v>
+        <v>0.000170289491109013</v>
       </c>
       <c r="P37" t="n">
-        <v>0.00409106536743519</v>
+        <v>0.00483903922364681</v>
       </c>
       <c r="Q37" t="n">
-        <v>-8008.650411665</v>
+        <v>-7794.2217892612</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/robust_garch_order/garch_order_robustness_results.xlsx
+++ b/outputs/robust_garch_order/garch_order_robustness_results.xlsx
@@ -511,24 +511,12 @@
       <c r="K2" t="n">
         <v>3123.19307180512</v>
       </c>
-      <c r="L2" t="n">
-        <v>0.00190202309250879</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.0336758039166346</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-3353.41529367087</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.000787374635689649</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.00940140126512556</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-6476.60836547599</v>
-      </c>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+      <c r="O2"/>
+      <c r="P2"/>
+      <c r="Q2"/>
     </row>
     <row r="3">
       <c r="A3" t="s">
@@ -564,24 +552,12 @@
       <c r="K3" t="n">
         <v>3115.64269286866</v>
       </c>
-      <c r="L3" t="n">
-        <v>0.00212346990156093</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.0358181174412756</v>
-      </c>
-      <c r="N3" t="n">
-        <v>-3143.43581143348</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.00100838541726636</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.0115249258690573</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-6259.07850430214</v>
-      </c>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+      <c r="O3"/>
+      <c r="P3"/>
+      <c r="Q3"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
@@ -699,24 +675,12 @@
       <c r="K6" t="n">
         <v>3119.15518848369</v>
       </c>
-      <c r="L6" t="n">
-        <v>73954604115547512896640024688666648082282648488228400840426688268468806862844</v>
-      </c>
-      <c r="M6" t="n">
-        <v>33566430128841934454466242006024644062</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-2243.50953093144</v>
-      </c>
-      <c r="O6" t="n">
-        <v>73954604115547512896640024688666648082282648488228400840426688268468806862844</v>
-      </c>
-      <c r="P6" t="n">
-        <v>33566430128841934454466242006024644062</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-5362.66471941514</v>
-      </c>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+      <c r="P6"/>
+      <c r="Q6"/>
     </row>
     <row r="7">
       <c r="A7" t="s">
@@ -752,24 +716,12 @@
       <c r="K7" t="n">
         <v>3127.64203958365</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.00192262907856386</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.0338906674335605</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-3251.28147427566</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.000807451500012366</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.009594104163205</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>-6378.92351385932</v>
-      </c>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+      <c r="Q7"/>
     </row>
     <row r="8">
       <c r="A8" t="s">
@@ -805,24 +757,12 @@
       <c r="K8" t="n">
         <v>3988.11779242861</v>
       </c>
-      <c r="L8" t="n">
-        <v>0.000613491365006613</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.0190700402540253</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-3284.9245422719</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.000256350148721334</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0.00577597837039016</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>-7273.04233470051</v>
-      </c>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="Q8"/>
     </row>
     <row r="9">
       <c r="A9" t="s">
@@ -858,24 +798,12 @@
       <c r="K9" t="n">
         <v>3984.37601355569</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.00078848325236476</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.021216328826141</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-2830.52981145011</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.000431408316804493</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0.00792852386689459</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>-6814.90582500581</v>
-      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+      <c r="P9"/>
+      <c r="Q9"/>
     </row>
     <row r="10">
       <c r="A10" t="s">
@@ -993,24 +921,12 @@
       <c r="K12" t="n">
         <v>3995.90239622051</v>
       </c>
-      <c r="L12" t="n">
-        <v>0.000641317267030788</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.0191562064930081</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-3268.95846878058</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.000284065898731319</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.00585409733064239</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-7264.86086500109</v>
-      </c>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+      <c r="P12"/>
+      <c r="Q12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
@@ -1046,24 +962,12 @@
       <c r="K13" t="n">
         <v>3984.71555365199</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.000776151654793395</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.0212299672662033</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-2937.08796428805</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.000419022393460054</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.00793687730769791</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>-6921.80351794004</v>
-      </c>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+      <c r="P13"/>
+      <c r="Q13"/>
     </row>
     <row r="14">
       <c r="A14" t="s">
@@ -1099,24 +1003,12 @@
       <c r="K14" t="n">
         <v>3775.86640303834</v>
       </c>
-      <c r="L14" t="n">
-        <v>0.0004998141245652</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.0159254468932027</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-131488.439699598</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.0000020736128414524</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.0000799600805808202</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>-135264.306102636</v>
-      </c>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+      <c r="Q14"/>
     </row>
     <row r="15">
       <c r="A15" t="s">
@@ -1152,24 +1044,12 @@
       <c r="K15" t="n">
         <v>3770.36100626239</v>
       </c>
-      <c r="L15" t="n">
-        <v>0.00109677471352657</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.0253004114502537</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-2868.01215754347</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.000599004647215737</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.00945489279954224</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-6638.37316380586</v>
-      </c>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+      <c r="P15"/>
+      <c r="Q15"/>
     </row>
     <row r="16">
       <c r="A16" t="s">
@@ -1205,24 +1085,12 @@
       <c r="K16" t="n">
         <v>3408.00015714302</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.00105920520602997</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.0221796122621299</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-2924.8039829289</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.000561809922211798</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.0063138165575046</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-6332.80414007192</v>
-      </c>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+      <c r="P16"/>
+      <c r="Q16"/>
     </row>
     <row r="17">
       <c r="A17" t="s">
@@ -1258,24 +1126,12 @@
       <c r="K17" t="n">
         <v>3755.12028192146</v>
       </c>
-      <c r="L17" t="n">
-        <v>0.000951124282123845</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.0232831771947112</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-3121.82013078468</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.000453576359427199</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.00743693371734754</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>-6876.94041270614</v>
-      </c>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+      <c r="P17"/>
+      <c r="Q17"/>
     </row>
     <row r="18">
       <c r="A18" t="s">
@@ -1311,24 +1167,12 @@
       <c r="K18" t="n">
         <v>3772.44626204037</v>
       </c>
-      <c r="L18" t="n">
-        <v>2780524339291910829066886220228280208886886644040002028468644208</v>
-      </c>
-      <c r="M18" t="n">
-        <v>7283944369916652698884882642408</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-2243.35888050633</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2780524339291910829066886220228280208886886644040002028468644208</v>
-      </c>
-      <c r="P18" t="n">
-        <v>7283944369916652698884882642408</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>-6015.8051425467</v>
-      </c>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+      <c r="P18"/>
+      <c r="Q18"/>
     </row>
     <row r="19">
       <c r="A19" t="s">
@@ -1364,24 +1208,12 @@
       <c r="K19" t="n">
         <v>3655.22998537484</v>
       </c>
-      <c r="L19" t="n">
-        <v>0.00136712307669806</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.0288430941535996</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-2759.78587448466</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.000869464809052282</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.0129974698227581</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>-6415.0158598595</v>
-      </c>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+      <c r="P19"/>
+      <c r="Q19"/>
     </row>
     <row r="20">
       <c r="A20" t="s">
@@ -1417,24 +1249,12 @@
       <c r="K20" t="n">
         <v>6117.39575516507</v>
       </c>
-      <c r="L20" t="n">
-        <v>0.0000684697136403873</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.00663650383089111</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-2609.55504894228</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0.0000463825758607848</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.00313485672482852</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-8726.95080410734</v>
-      </c>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+      <c r="P20"/>
+      <c r="Q20"/>
     </row>
     <row r="21">
       <c r="A21" t="s">
@@ -1470,24 +1290,12 @@
       <c r="K21" t="n">
         <v>6043.9607137356</v>
       </c>
-      <c r="L21" t="n">
-        <v>0.0000864325152929873</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0.00739260999190352</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-2532.0885718045</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.0000643499973832386</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0.00389146172046463</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>-8576.0492855401</v>
-      </c>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+      <c r="P21"/>
+      <c r="Q21"/>
     </row>
     <row r="22">
       <c r="A22" t="s">
@@ -1605,24 +1413,12 @@
       <c r="K24" t="n">
         <v>6112.72531273013</v>
       </c>
-      <c r="L24" t="n">
-        <v>0.0000604371607791775</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.00611768541025055</v>
-      </c>
-      <c r="N24" t="n">
-        <v>-2702.75678222766</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0.0000383529833115843</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.00261633882049544</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>-8815.48209495779</v>
-      </c>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+      <c r="P24"/>
+      <c r="Q24"/>
     </row>
     <row r="25">
       <c r="A25" t="s">
@@ -1658,24 +1454,12 @@
       <c r="K25" t="n">
         <v>6063.57101232905</v>
       </c>
-      <c r="L25" t="n">
-        <v>0.0000644126701447323</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.00631364585314944</v>
-      </c>
-      <c r="N25" t="n">
-        <v>-2660.81703282341</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.0000423313658119837</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0.00281266420154376</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>-8724.38804515245</v>
-      </c>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+      <c r="P25"/>
+      <c r="Q25"/>
     </row>
     <row r="26">
       <c r="A26" t="s">
@@ -1711,24 +1495,12 @@
       <c r="K26" t="n">
         <v>5850.6497879914</v>
       </c>
-      <c r="L26" t="n">
-        <v>0.0000792105359641043</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.00679725210034686</v>
-      </c>
-      <c r="N26" t="n">
-        <v>-2778.9253468018</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0.0000448890207787151</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0.0024853632148878</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>-8629.5751347932</v>
-      </c>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
     </row>
     <row r="27">
       <c r="A27" t="s">
@@ -1764,24 +1536,12 @@
       <c r="K27" t="n">
         <v>5884.64928742832</v>
       </c>
-      <c r="L27" t="n">
-        <v>0.000067380779782448</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.00634640020093867</v>
-      </c>
-      <c r="N27" t="n">
-        <v>-3065.16045477383</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0.0000330590949378084</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0.00203474106675785</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>-8949.80974220215</v>
-      </c>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
     </row>
     <row r="28">
       <c r="A28" t="s">
@@ -1899,24 +1659,12 @@
       <c r="K30" t="n">
         <v>5849.22822585094</v>
       </c>
-      <c r="L30" t="n">
-        <v>0.0000815454702069571</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0.00697096949283593</v>
-      </c>
-      <c r="N30" t="n">
-        <v>-2871.78512943571</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0.0000472239566429413</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0.00265907429275529</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>-8721.01335528665</v>
-      </c>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+      <c r="P30"/>
+      <c r="Q30"/>
     </row>
     <row r="31">
       <c r="A31" t="s">
@@ -1952,24 +1700,12 @@
       <c r="K31" t="n">
         <v>5884.56321600794</v>
       </c>
-      <c r="L31" t="n">
-        <v>0.000069142799401713</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0.00642797830720931</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-3098.7258568091</v>
-      </c>
-      <c r="O31" t="n">
-        <v>0.0000348209715300089</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0.00211641624487703</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>-8983.28907281704</v>
-      </c>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+      <c r="P31"/>
+      <c r="Q31"/>
     </row>
     <row r="32">
       <c r="A32" t="s">
@@ -2005,24 +1741,12 @@
       <c r="K32" t="n">
         <v>5029.22619018546</v>
       </c>
-      <c r="L32" t="n">
-        <v>0.000217388689408545</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.0116034393963345</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-3002.34134634544</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0.000119436401905049</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.00398276620866208</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>-8031.5675365309</v>
-      </c>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+      <c r="P32"/>
+      <c r="Q32"/>
     </row>
     <row r="33">
       <c r="A33" t="s">
@@ -2058,24 +1782,12 @@
       <c r="K33" t="n">
         <v>5035.98410313405</v>
       </c>
-      <c r="L33" t="n">
-        <v>0.000205037519290683</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.0111674428327975</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-2965.20459282729</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.000107086133327328</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0.00354718852932196</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>-8001.18869596134</v>
-      </c>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+      <c r="P33"/>
+      <c r="Q33"/>
     </row>
     <row r="34">
       <c r="A34" t="s">
@@ -2193,24 +1905,12 @@
       <c r="K36" t="n">
         <v>5044.08121193212</v>
       </c>
-      <c r="L36" t="n">
-        <v>0.000273135773302722</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.0125787898977313</v>
-      </c>
-      <c r="N36" t="n">
-        <v>-2728.49170102051</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0.000175152839246049</v>
-      </c>
-      <c r="P36" t="n">
-        <v>0.00495070862993907</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>-7772.57291295263</v>
-      </c>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
     </row>
     <row r="37">
       <c r="A37" t="s">
@@ -2246,24 +1946,12 @@
       <c r="K37" t="n">
         <v>5051.80195164274</v>
       </c>
-      <c r="L37" t="n">
-        <v>0.000268271765220214</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.0124670111471548</v>
-      </c>
-      <c r="N37" t="n">
-        <v>-2742.41983761846</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0.000170289491109013</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0.00483903922364681</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>-7794.2217892612</v>
-      </c>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/outputs/robust_garch_order/garch_order_robustness_results.xlsx
+++ b/outputs/robust_garch_order/garch_order_robustness_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">asset</t>
   </si>
@@ -86,6 +86,15 @@
     <t xml:space="preserve">MSFT</t>
   </si>
   <si>
+    <t xml:space="preserve">PG</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WMT</t>
+  </si>
+  <si>
     <t xml:space="preserve">AMZN</t>
   </si>
   <si>
@@ -95,7 +104,16 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
+    <t xml:space="preserve">GBPCNY</t>
+  </si>
+  <si>
     <t xml:space="preserve">USDZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GBPZAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EURZAR</t>
   </si>
 </sst>
 </file>
@@ -983,25 +1001,25 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.60414114225732</v>
+        <v>-6.39182107974727</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.61433903243915</v>
+        <v>-6.39997939189274</v>
       </c>
       <c r="H14" t="n">
-        <v>6774.23536058824</v>
+        <v>9392.76976790665</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000497740511723748</v>
+        <v>0.000173027768537589</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0158454868126219</v>
+        <v>0.00873820806998403</v>
       </c>
       <c r="K14" t="n">
-        <v>3775.86640303834</v>
+        <v>4511.97269537235</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
@@ -1027,22 +1045,22 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.92230222145556</v>
+        <v>-6.52162145575324</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.93453968967376</v>
+        <v>-6.53385892397145</v>
       </c>
       <c r="H15" t="n">
-        <v>7244.96972475141</v>
+        <v>9591.17104146612</v>
       </c>
       <c r="I15" t="n">
-        <v>0.000497770066310838</v>
+        <v>0.000173039430930777</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0158455186507115</v>
+        <v>0.00874119201201824</v>
       </c>
       <c r="K15" t="n">
-        <v>3770.36100626239</v>
+        <v>4599.25542302957</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -1062,28 +1080,28 @@
         <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>-4.66126790841841</v>
+        <v>-6.40127332888572</v>
       </c>
       <c r="G16" t="n">
-        <v>-4.67554495467298</v>
+        <v>-6.41147121906755</v>
       </c>
       <c r="H16" t="n">
-        <v>6866.02444850527</v>
+        <v>9410.6282783721</v>
       </c>
       <c r="I16" t="n">
-        <v>0.00049739528381817</v>
+        <v>0.000173101279562829</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0158657957046253</v>
+        <v>0.00875102013775755</v>
       </c>
       <c r="K16" t="n">
-        <v>3408.00015714302</v>
+        <v>4579.15323567698</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -1109,22 +1127,22 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>-4.94604003763756</v>
+        <v>-6.5319140533739</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.96031708389214</v>
+        <v>-6.54619109962847</v>
       </c>
       <c r="H17" t="n">
-        <v>7283.78516206976</v>
+        <v>9610.26234315497</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000497547922696646</v>
+        <v>0.000173101265083896</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0158462434773637</v>
+        <v>0.00875101830170995</v>
       </c>
       <c r="K17" t="n">
-        <v>3755.12028192146</v>
+        <v>4438.27689190541</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -1144,28 +1162,28 @@
         <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.61564666631265</v>
+        <v>-6.39488808544956</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.62992371256722</v>
+        <v>-6.4050859756314</v>
       </c>
       <c r="H18" t="n">
-        <v>6799.09808633611</v>
+        <v>9401.26112625126</v>
       </c>
       <c r="I18" t="n">
-        <v>0.00049773766393544</v>
+        <v>0.000173078430269965</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0158454882074985</v>
+        <v>0.00874793998571388</v>
       </c>
       <c r="K18" t="n">
-        <v>3772.44626204037</v>
+        <v>4473.98355355345</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -1191,22 +1209,22 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.92784796932361</v>
+        <v>-6.52439191144956</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.94212501557818</v>
+        <v>-6.53866895770414</v>
       </c>
       <c r="H19" t="n">
-        <v>7257.09739785319</v>
+        <v>9599.22736095197</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000497658267645776</v>
+        <v>0.000173075547909668</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0158456243308415</v>
+        <v>0.00874751947582641</v>
       </c>
       <c r="K19" t="n">
-        <v>3655.22998537484</v>
+        <v>4589.33776613516</v>
       </c>
       <c r="L19"/>
       <c r="M19"/>
@@ -1232,22 +1250,22 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>-7.40778478998216</v>
+        <v>-5.16357918424433</v>
       </c>
       <c r="G20" t="n">
-        <v>-7.41594310212763</v>
+        <v>-5.1717374963898</v>
       </c>
       <c r="H20" t="n">
-        <v>10883.1885308212</v>
+        <v>7590.93890720383</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0000220871377796025</v>
+        <v>0.000427009808579778</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00350164710606259</v>
+        <v>0.0148885450504351</v>
       </c>
       <c r="K20" t="n">
-        <v>6117.39575516507</v>
+        <v>3880.57558501832</v>
       </c>
       <c r="L20"/>
       <c r="M20"/>
@@ -1273,22 +1291,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>-7.45675061975955</v>
+        <v>-5.26867524332051</v>
       </c>
       <c r="G21" t="n">
-        <v>-7.46898808797776</v>
+        <v>-5.28091271153872</v>
       </c>
       <c r="H21" t="n">
-        <v>10963.0055250634</v>
+        <v>7753.0989478273</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0000220825179097488</v>
+        <v>0.000427009099004181</v>
       </c>
       <c r="J21" t="n">
-        <v>0.00350114827143889</v>
+        <v>0.0148885873227819</v>
       </c>
       <c r="K21" t="n">
-        <v>6043.9607137356</v>
+        <v>3860.22807488225</v>
       </c>
       <c r="L21"/>
       <c r="M21"/>
@@ -1308,28 +1326,28 @@
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>-7.40495350240917</v>
+        <v>-5.19669226616628</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.41923054866374</v>
+        <v>-5.20689015634812</v>
       </c>
       <c r="H22" t="n">
-        <v>10891.0112148897</v>
+        <v>7643.50785936269</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0000220810159775232</v>
+        <v>0.000427041701878454</v>
       </c>
       <c r="J22" t="n">
-        <v>0.00350093835243901</v>
+        <v>0.0148944310725243</v>
       </c>
       <c r="K22" t="n">
-        <v>5981.44223636607</v>
+        <v>3872.41989278354</v>
       </c>
       <c r="L22"/>
       <c r="M22"/>
@@ -1355,22 +1373,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.45625481489064</v>
+        <v>-5.29241997443249</v>
       </c>
       <c r="G23" t="n">
-        <v>-7.47053186114522</v>
+        <v>-5.30669702068706</v>
       </c>
       <c r="H23" t="n">
-        <v>10966.2702403</v>
+        <v>7791.92452934792</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0000220789981361393</v>
+        <v>0.000427013408151869</v>
       </c>
       <c r="J23" t="n">
-        <v>0.00350061520003008</v>
+        <v>0.0148922032540321</v>
       </c>
       <c r="K23" t="n">
-        <v>6153.91647861519</v>
+        <v>3745.30658587702</v>
       </c>
       <c r="L23"/>
       <c r="M23"/>
@@ -1396,22 +1414,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>-7.40580510083685</v>
+        <v>-5.17318773502243</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.41600299101869</v>
+        <v>-5.18338562520427</v>
       </c>
       <c r="H24" t="n">
-        <v>10884.2763878244</v>
+        <v>7609.02671217467</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0000220841774675933</v>
+        <v>0.000427001068326632</v>
       </c>
       <c r="J24" t="n">
-        <v>0.00350134658975511</v>
+        <v>0.0148904087713498</v>
       </c>
       <c r="K24" t="n">
-        <v>6112.72531273013</v>
+        <v>3853.70930192326</v>
       </c>
       <c r="L24"/>
       <c r="M24"/>
@@ -1437,22 +1455,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>-7.45419380852886</v>
+        <v>-5.27568743839133</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.46847085478344</v>
+        <v>-5.28996448464591</v>
       </c>
       <c r="H25" t="n">
-        <v>10963.2467439673</v>
+        <v>7767.37789897555</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0000220813043327487</v>
+        <v>0.000427002105418983</v>
       </c>
       <c r="J25" t="n">
-        <v>0.00350098165160568</v>
+        <v>0.0148906642105145</v>
       </c>
       <c r="K25" t="n">
-        <v>6063.57101232905</v>
+        <v>3885.3361056724</v>
       </c>
       <c r="L25"/>
       <c r="M25"/>
@@ -1478,22 +1496,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.47350817319533</v>
+        <v>-6.08014781948621</v>
       </c>
       <c r="G26" t="n">
-        <v>-7.4816664853408</v>
+        <v>-6.08830613163168</v>
       </c>
       <c r="H26" t="n">
-        <v>10979.604733995</v>
+        <v>8935.54509510367</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0000343215151853892</v>
+        <v>0.000203936033515385</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00431188888545906</v>
+        <v>0.00920850200164572</v>
       </c>
       <c r="K26" t="n">
-        <v>5850.6497879914</v>
+        <v>4453.71610324234</v>
       </c>
       <c r="L26"/>
       <c r="M26"/>
@@ -1519,22 +1537,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>-7.52948011214007</v>
+        <v>-6.22168721079134</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.54171758035828</v>
+        <v>-6.23392467900954</v>
       </c>
       <c r="H27" t="n">
-        <v>11069.6996903856</v>
+        <v>9151.167504107</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0000343216848446396</v>
+        <v>0.000203930400296643</v>
       </c>
       <c r="J27" t="n">
-        <v>0.00431165913418082</v>
+        <v>0.0092081932084695</v>
       </c>
       <c r="K27" t="n">
-        <v>5884.64928742832</v>
+        <v>4452.99738386152</v>
       </c>
       <c r="L27"/>
       <c r="M27"/>
@@ -1560,22 +1578,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>-7.47562123655602</v>
+        <v>-6.08805526132953</v>
       </c>
       <c r="G28" t="n">
-        <v>-7.4898982828106</v>
+        <v>-6.1023323075841</v>
       </c>
       <c r="H28" t="n">
-        <v>10994.6807808831</v>
+        <v>8959.12149522587</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0000343228481663364</v>
+        <v>0.000203988863102013</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00431286081058617</v>
+        <v>0.00921094882594286</v>
       </c>
       <c r="K28" t="n">
-        <v>5806.24216921478</v>
+        <v>4460.64205783928</v>
       </c>
       <c r="L28"/>
       <c r="M28"/>
@@ -1601,22 +1619,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>-7.53495360155169</v>
+        <v>-6.23014234000606</v>
       </c>
       <c r="G29" t="n">
-        <v>-7.54923064780626</v>
+        <v>-6.24441938626063</v>
       </c>
       <c r="H29" t="n">
-        <v>11081.7213603318</v>
+        <v>9167.56323964435</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0000343230886993207</v>
+        <v>0.000203962093851359</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00431295439035695</v>
+        <v>0.00920976802727746</v>
       </c>
       <c r="K29" t="n">
-        <v>5868.82638053184</v>
+        <v>4378.96069234667</v>
       </c>
       <c r="L29"/>
       <c r="M29"/>
@@ -1636,28 +1654,28 @@
         <v>19</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>-7.47078512447476</v>
+        <v>-6.08126240318086</v>
       </c>
       <c r="G30" t="n">
-        <v>-7.4809830146566</v>
+        <v>-6.09553944943544</v>
       </c>
       <c r="H30" t="n">
-        <v>10979.6020825012</v>
+        <v>8949.15637232179</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0000343215135640158</v>
+        <v>0.000203962122638318</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00431189520008064</v>
+        <v>0.00920976930847519</v>
       </c>
       <c r="K30" t="n">
-        <v>5849.22822585094</v>
+        <v>4452.28198275149</v>
       </c>
       <c r="L30"/>
       <c r="M30"/>
@@ -1683,22 +1701,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-7.5269216122679</v>
+        <v>-6.22092445790455</v>
       </c>
       <c r="G31" t="n">
-        <v>-7.54119865852247</v>
+        <v>-6.23520150415912</v>
       </c>
       <c r="H31" t="n">
-        <v>11069.9384320525</v>
+        <v>9154.04060660143</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0000343218278717042</v>
+        <v>0.000203955604340564</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00431156206233229</v>
+        <v>0.00920947343569041</v>
       </c>
       <c r="K31" t="n">
-        <v>5884.56321600794</v>
+        <v>4441.35175990047</v>
       </c>
       <c r="L31"/>
       <c r="M31"/>
@@ -1721,25 +1739,25 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.27551453014706</v>
+        <v>-4.60414114225732</v>
       </c>
       <c r="G32" t="n">
-        <v>-6.28367284229253</v>
+        <v>-4.61433903243915</v>
       </c>
       <c r="H32" t="n">
-        <v>9222.14805964314</v>
+        <v>6774.23536058824</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0000979522875034966</v>
+        <v>0.000497740511723748</v>
       </c>
       <c r="J32" t="n">
-        <v>0.00762067318767246</v>
+        <v>0.0158454868126219</v>
       </c>
       <c r="K32" t="n">
-        <v>5029.22619018546</v>
+        <v>3775.86640303834</v>
       </c>
       <c r="L32"/>
       <c r="M32"/>
@@ -1765,22 +1783,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>-6.30779688142885</v>
+        <v>-4.92230222145556</v>
       </c>
       <c r="G33" t="n">
-        <v>-6.32003434964706</v>
+        <v>-4.93453968967376</v>
       </c>
       <c r="H33" t="n">
-        <v>9277.49039093223</v>
+        <v>7244.96972475141</v>
       </c>
       <c r="I33" t="n">
-        <v>0.0000979513859633547</v>
+        <v>0.000497770066310838</v>
       </c>
       <c r="J33" t="n">
-        <v>0.00762025430347554</v>
+        <v>0.0158455186507115</v>
       </c>
       <c r="K33" t="n">
-        <v>5035.98410313405</v>
+        <v>3770.36100626239</v>
       </c>
       <c r="L33"/>
       <c r="M33"/>
@@ -1803,25 +1821,25 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>-6.27772262421088</v>
+        <v>-4.66126790841841</v>
       </c>
       <c r="G34" t="n">
-        <v>-6.29403924850182</v>
+        <v>-4.67554495467298</v>
       </c>
       <c r="H34" t="n">
-        <v>9241.35557755217</v>
+        <v>6866.02444850527</v>
       </c>
       <c r="I34" t="n">
-        <v>0.0000980106546343087</v>
+        <v>0.00049739528381817</v>
       </c>
       <c r="J34" t="n">
-        <v>0.00763212416347733</v>
+        <v>0.0158657957046253</v>
       </c>
       <c r="K34" t="n">
-        <v>5038.02723708611</v>
+        <v>3408.00015714302</v>
       </c>
       <c r="L34"/>
       <c r="M34"/>
@@ -1847,22 +1865,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>-6.3083005107007</v>
+        <v>-4.94604003763756</v>
       </c>
       <c r="G35" t="n">
-        <v>-6.32257755695527</v>
+        <v>-4.96031708389214</v>
       </c>
       <c r="H35" t="n">
-        <v>9282.22127605338</v>
+        <v>7283.78516206976</v>
       </c>
       <c r="I35" t="n">
-        <v>0.0000979932584494563</v>
+        <v>0.000497547922696646</v>
       </c>
       <c r="J35" t="n">
-        <v>0.00762968525547159</v>
+        <v>0.0158462434773637</v>
       </c>
       <c r="K35" t="n">
-        <v>5049.20315589203</v>
+        <v>3755.12028192146</v>
       </c>
       <c r="L35"/>
       <c r="M35"/>
@@ -1882,28 +1900,28 @@
         <v>19</v>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>-6.27645225149923</v>
+        <v>-4.61564666631265</v>
       </c>
       <c r="G36" t="n">
-        <v>-6.28665014168107</v>
+        <v>-4.62992371256722</v>
       </c>
       <c r="H36" t="n">
-        <v>9227.51575784613</v>
+        <v>6799.09808633611</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0000979829340566733</v>
+        <v>0.00049773766393544</v>
       </c>
       <c r="J36" t="n">
-        <v>0.00762808126779227</v>
+        <v>0.0158454882074985</v>
       </c>
       <c r="K36" t="n">
-        <v>5044.08121193212</v>
+        <v>3772.44626204037</v>
       </c>
       <c r="L36"/>
       <c r="M36"/>
@@ -1929,22 +1947,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.30940745543358</v>
+        <v>-4.92784796932361</v>
       </c>
       <c r="G37" t="n">
-        <v>-6.32368450168815</v>
+        <v>-4.94212501557818</v>
       </c>
       <c r="H37" t="n">
-        <v>9283.84516397652</v>
+        <v>7257.09739785319</v>
       </c>
       <c r="I37" t="n">
-        <v>0.0000979822741112018</v>
+        <v>0.000497658267645776</v>
       </c>
       <c r="J37" t="n">
-        <v>0.00762797192350798</v>
+        <v>0.0158456243308415</v>
       </c>
       <c r="K37" t="n">
-        <v>5051.80195164274</v>
+        <v>3655.22998537484</v>
       </c>
       <c r="L37"/>
       <c r="M37"/>
@@ -1953,6 +1971,1482 @@
       <c r="P37"/>
       <c r="Q37"/>
     </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" t="s">
+        <v>19</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-7.40778478998216</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-7.41594310212763</v>
+      </c>
+      <c r="H38" t="n">
+        <v>10883.1885308212</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0000220871377796025</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.00350164710606259</v>
+      </c>
+      <c r="K38" t="n">
+        <v>6117.39575516507</v>
+      </c>
+      <c r="L38"/>
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+      <c r="P38"/>
+      <c r="Q38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-7.45675061975955</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-7.46898808797776</v>
+      </c>
+      <c r="H39" t="n">
+        <v>10963.0055250634</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0000220825179097488</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.00350114827143889</v>
+      </c>
+      <c r="K39" t="n">
+        <v>6043.9607137356</v>
+      </c>
+      <c r="L39"/>
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+      <c r="P39"/>
+      <c r="Q39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>28</v>
+      </c>
+      <c r="B40" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" t="s">
+        <v>19</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-7.40495350240917</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-7.41923054866374</v>
+      </c>
+      <c r="H40" t="n">
+        <v>10891.0112148897</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.0000220810159775232</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.00350093835243901</v>
+      </c>
+      <c r="K40" t="n">
+        <v>5981.44223636607</v>
+      </c>
+      <c r="L40"/>
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+      <c r="P40"/>
+      <c r="Q40"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>28</v>
+      </c>
+      <c r="B41" t="s">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-7.45625481489064</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-7.47053186114522</v>
+      </c>
+      <c r="H41" t="n">
+        <v>10966.2702403</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.0000220789981361393</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.00350061520003008</v>
+      </c>
+      <c r="K41" t="n">
+        <v>6153.91647861519</v>
+      </c>
+      <c r="L41"/>
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+      <c r="P41"/>
+      <c r="Q41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>19</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-7.40580510083685</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-7.41600299101869</v>
+      </c>
+      <c r="H42" t="n">
+        <v>10884.2763878244</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.0000220841774675933</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.00350134658975511</v>
+      </c>
+      <c r="K42" t="n">
+        <v>6112.72531273013</v>
+      </c>
+      <c r="L42"/>
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+      <c r="P42"/>
+      <c r="Q42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-7.45419380852886</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-7.46847085478344</v>
+      </c>
+      <c r="H43" t="n">
+        <v>10963.2467439673</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.0000220813043327487</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.00350098165160568</v>
+      </c>
+      <c r="K43" t="n">
+        <v>6063.57101232905</v>
+      </c>
+      <c r="L43"/>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
+      <c r="P43"/>
+      <c r="Q43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-7.47350817319533</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-7.4816664853408</v>
+      </c>
+      <c r="H44" t="n">
+        <v>10979.604733995</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.0000343215151853892</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.00431188888545906</v>
+      </c>
+      <c r="K44" t="n">
+        <v>5850.6497879914</v>
+      </c>
+      <c r="L44"/>
+      <c r="M44"/>
+      <c r="N44"/>
+      <c r="O44"/>
+      <c r="P44"/>
+      <c r="Q44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>29</v>
+      </c>
+      <c r="B45" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" t="s">
+        <v>20</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-7.52948011214007</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-7.54171758035828</v>
+      </c>
+      <c r="H45" t="n">
+        <v>11069.6996903856</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.0000343216848446396</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.00431165913418082</v>
+      </c>
+      <c r="K45" t="n">
+        <v>5884.64928742832</v>
+      </c>
+      <c r="L45"/>
+      <c r="M45"/>
+      <c r="N45"/>
+      <c r="O45"/>
+      <c r="P45"/>
+      <c r="Q45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+      <c r="B46" t="s">
+        <v>21</v>
+      </c>
+      <c r="C46" t="s">
+        <v>19</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-7.47562123655602</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-7.4898982828106</v>
+      </c>
+      <c r="H46" t="n">
+        <v>10994.6807808831</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.0000343228481663364</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.00431286081058617</v>
+      </c>
+      <c r="K46" t="n">
+        <v>5806.24216921478</v>
+      </c>
+      <c r="L46"/>
+      <c r="M46"/>
+      <c r="N46"/>
+      <c r="O46"/>
+      <c r="P46"/>
+      <c r="Q46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>29</v>
+      </c>
+      <c r="B47" t="s">
+        <v>21</v>
+      </c>
+      <c r="C47" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-7.53495360155169</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-7.54923064780626</v>
+      </c>
+      <c r="H47" t="n">
+        <v>11081.7213603318</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.0000343230886993207</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.00431295439035695</v>
+      </c>
+      <c r="K47" t="n">
+        <v>5868.82638053184</v>
+      </c>
+      <c r="L47"/>
+      <c r="M47"/>
+      <c r="N47"/>
+      <c r="O47"/>
+      <c r="P47"/>
+      <c r="Q47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>29</v>
+      </c>
+      <c r="B48" t="s">
+        <v>22</v>
+      </c>
+      <c r="C48" t="s">
+        <v>19</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-7.47078512447476</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-7.4809830146566</v>
+      </c>
+      <c r="H48" t="n">
+        <v>10979.6020825012</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.0000343215135640158</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.00431189520008064</v>
+      </c>
+      <c r="K48" t="n">
+        <v>5849.22822585094</v>
+      </c>
+      <c r="L48"/>
+      <c r="M48"/>
+      <c r="N48"/>
+      <c r="O48"/>
+      <c r="P48"/>
+      <c r="Q48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>29</v>
+      </c>
+      <c r="B49" t="s">
+        <v>22</v>
+      </c>
+      <c r="C49" t="s">
+        <v>20</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-7.5269216122679</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-7.54119865852247</v>
+      </c>
+      <c r="H49" t="n">
+        <v>11069.9384320525</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.0000343218278717042</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.00431156206233229</v>
+      </c>
+      <c r="K49" t="n">
+        <v>5884.56321600794</v>
+      </c>
+      <c r="L49"/>
+      <c r="M49"/>
+      <c r="N49"/>
+      <c r="O49"/>
+      <c r="P49"/>
+      <c r="Q49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>30</v>
+      </c>
+      <c r="B50" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" t="s">
+        <v>19</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-7.44504153616433</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-7.4531998483098</v>
+      </c>
+      <c r="H50" t="n">
+        <v>10937.8441774705</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.000030470814016406</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.00408182322711205</v>
+      </c>
+      <c r="K50" t="n">
+        <v>5837.19208338236</v>
+      </c>
+      <c r="L50"/>
+      <c r="M50"/>
+      <c r="N50"/>
+      <c r="O50"/>
+      <c r="P50"/>
+      <c r="Q50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" t="s">
+        <v>20</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-7.49221066754127</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-7.50444813575948</v>
+      </c>
+      <c r="H51" t="n">
+        <v>11015.0254151592</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.0000304678767962828</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.00408109018837926</v>
+      </c>
+      <c r="K51" t="n">
+        <v>5958.25992226711</v>
+      </c>
+      <c r="L51"/>
+      <c r="M51"/>
+      <c r="N51"/>
+      <c r="O51"/>
+      <c r="P51"/>
+      <c r="Q51"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>30</v>
+      </c>
+      <c r="B52" t="s">
+        <v>21</v>
+      </c>
+      <c r="C52" t="s">
+        <v>19</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-7.44211154699923</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-7.45230943718107</v>
+      </c>
+      <c r="H52" t="n">
+        <v>10937.5379443446</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.0000304857968667413</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.00408488160823153</v>
+      </c>
+      <c r="K52" t="n">
+        <v>5780.83066380907</v>
+      </c>
+      <c r="L52"/>
+      <c r="M52"/>
+      <c r="N52"/>
+      <c r="O52"/>
+      <c r="P52"/>
+      <c r="Q52"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>30</v>
+      </c>
+      <c r="B53" t="s">
+        <v>21</v>
+      </c>
+      <c r="C53" t="s">
+        <v>20</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-7.49888455121143</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-7.51316159746601</v>
+      </c>
+      <c r="H53" t="n">
+        <v>11028.8080634826</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.0000304953170051174</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.00408651669944771</v>
+      </c>
+      <c r="K53" t="n">
+        <v>5977.6734536854</v>
+      </c>
+      <c r="L53"/>
+      <c r="M53"/>
+      <c r="N53"/>
+      <c r="O53"/>
+      <c r="P53"/>
+      <c r="Q53"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>30</v>
+      </c>
+      <c r="B54" t="s">
+        <v>22</v>
+      </c>
+      <c r="C54" t="s">
+        <v>19</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-7.44256812678184</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-7.45276601696368</v>
+      </c>
+      <c r="H54" t="n">
+        <v>10938.2077468857</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.0000304735409074575</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.00408245461970814</v>
+      </c>
+      <c r="K54" t="n">
+        <v>5854.04064867584</v>
+      </c>
+      <c r="L54"/>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55" t="s">
+        <v>22</v>
+      </c>
+      <c r="C55" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-7.49257558127722</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-7.5068526275318</v>
+      </c>
+      <c r="H55" t="n">
+        <v>11019.5528045891</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.0000304734809874528</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.00408244119127097</v>
+      </c>
+      <c r="K55" t="n">
+        <v>5976.66516051836</v>
+      </c>
+      <c r="L55"/>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55"/>
+      <c r="Q55"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>31</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-6.27551453014706</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-6.28367284229253</v>
+      </c>
+      <c r="H56" t="n">
+        <v>9222.14805964314</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.0000979522875034966</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.00762067318767246</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5029.22619018546</v>
+      </c>
+      <c r="L56"/>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>31</v>
+      </c>
+      <c r="B57" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-6.30779688142885</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-6.32003434964706</v>
+      </c>
+      <c r="H57" t="n">
+        <v>9277.49039093223</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.0000979513859633547</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.00762025430347554</v>
+      </c>
+      <c r="K57" t="n">
+        <v>5035.98410313405</v>
+      </c>
+      <c r="L57"/>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>31</v>
+      </c>
+      <c r="B58" t="s">
+        <v>21</v>
+      </c>
+      <c r="C58" t="s">
+        <v>19</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-6.27772262421088</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-6.29403924850182</v>
+      </c>
+      <c r="H58" t="n">
+        <v>9241.35557755217</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.0000980106546343087</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.00763212416347733</v>
+      </c>
+      <c r="K58" t="n">
+        <v>5038.02723708611</v>
+      </c>
+      <c r="L58"/>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>31</v>
+      </c>
+      <c r="B59" t="s">
+        <v>21</v>
+      </c>
+      <c r="C59" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-6.3083005107007</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-6.32257755695527</v>
+      </c>
+      <c r="H59" t="n">
+        <v>9282.22127605338</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.0000979932584494563</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.00762968525547159</v>
+      </c>
+      <c r="K59" t="n">
+        <v>5049.20315589203</v>
+      </c>
+      <c r="L59"/>
+      <c r="M59"/>
+      <c r="N59"/>
+      <c r="O59"/>
+      <c r="P59"/>
+      <c r="Q59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>31</v>
+      </c>
+      <c r="B60" t="s">
+        <v>22</v>
+      </c>
+      <c r="C60" t="s">
+        <v>19</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-6.27645225149923</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-6.28665014168107</v>
+      </c>
+      <c r="H60" t="n">
+        <v>9227.51575784613</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.0000979829340566733</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.00762808126779227</v>
+      </c>
+      <c r="K60" t="n">
+        <v>5044.08121193212</v>
+      </c>
+      <c r="L60"/>
+      <c r="M60"/>
+      <c r="N60"/>
+      <c r="O60"/>
+      <c r="P60"/>
+      <c r="Q60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" t="s">
+        <v>20</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-6.30940745543358</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-6.32368450168815</v>
+      </c>
+      <c r="H61" t="n">
+        <v>9283.84516397652</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.0000979822741112018</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.00762797192350798</v>
+      </c>
+      <c r="K61" t="n">
+        <v>5051.80195164274</v>
+      </c>
+      <c r="L61"/>
+      <c r="M61"/>
+      <c r="N61"/>
+      <c r="O61"/>
+      <c r="P61"/>
+      <c r="Q61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>32</v>
+      </c>
+      <c r="B62" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" t="s">
+        <v>19</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-6.4297097377123</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-6.43786804985777</v>
+      </c>
+      <c r="H62" t="n">
+        <v>9448.35242914135</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.0000803339350240065</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.00675909651890509</v>
+      </c>
+      <c r="K62" t="n">
+        <v>5177.3961190569</v>
+      </c>
+      <c r="L62"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="P62"/>
+      <c r="Q62"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-6.47125091630012</v>
+      </c>
+      <c r="G63" t="n">
+        <v>-6.48348838451832</v>
+      </c>
+      <c r="H63" t="n">
+        <v>9517.27746008838</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.0000803359015911899</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.00675966731397236</v>
+      </c>
+      <c r="K63" t="n">
+        <v>5182.81281607738</v>
+      </c>
+      <c r="L63"/>
+      <c r="M63"/>
+      <c r="N63"/>
+      <c r="O63"/>
+      <c r="P63"/>
+      <c r="Q63"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>32</v>
+      </c>
+      <c r="B64" t="s">
+        <v>21</v>
+      </c>
+      <c r="C64" t="s">
+        <v>19</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" t="n">
+        <v>-6.42876217773409</v>
+      </c>
+      <c r="G64" t="n">
+        <v>-6.43896006791593</v>
+      </c>
+      <c r="H64" t="n">
+        <v>9450.95441963267</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.0000803511132607742</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.00676255786756616</v>
+      </c>
+      <c r="K64" t="n">
+        <v>5156.01109998202</v>
+      </c>
+      <c r="L64"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="P64"/>
+      <c r="Q64"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>32</v>
+      </c>
+      <c r="B65" t="s">
+        <v>21</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" t="n">
+        <v>-6.46738664429885</v>
+      </c>
+      <c r="G65" t="n">
+        <v>-6.48166369055342</v>
+      </c>
+      <c r="H65" t="n">
+        <v>9515.60063404187</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.0000803534404058461</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.00676289567888918</v>
+      </c>
+      <c r="K65" t="n">
+        <v>5200.12096009357</v>
+      </c>
+      <c r="L65"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="P65"/>
+      <c r="Q65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>32</v>
+      </c>
+      <c r="B66" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" t="s">
+        <v>19</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" t="n">
+        <v>-6.42879392055159</v>
+      </c>
+      <c r="G66" t="n">
+        <v>-6.43899181073343</v>
+      </c>
+      <c r="H66" t="n">
+        <v>9451.00098634594</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.0000803480888241652</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.00676209152823362</v>
+      </c>
+      <c r="K66" t="n">
+        <v>5188.44625830715</v>
+      </c>
+      <c r="L66"/>
+      <c r="M66"/>
+      <c r="N66"/>
+      <c r="O66"/>
+      <c r="P66"/>
+      <c r="Q66"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>32</v>
+      </c>
+      <c r="B67" t="s">
+        <v>22</v>
+      </c>
+      <c r="C67" t="s">
+        <v>20</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" t="n">
+        <v>-6.47002620910434</v>
+      </c>
+      <c r="G67" t="n">
+        <v>-6.48430325535892</v>
+      </c>
+      <c r="H67" t="n">
+        <v>9519.47287561153</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.000080347911668574</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.00676206307276652</v>
+      </c>
+      <c r="K67" t="n">
+        <v>5196.92843629582</v>
+      </c>
+      <c r="L67"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="P67"/>
+      <c r="Q67"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C68" t="s">
+        <v>19</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" t="n">
+        <v>-6.46105501407736</v>
+      </c>
+      <c r="G68" t="n">
+        <v>-6.46921332622283</v>
+      </c>
+      <c r="H68" t="n">
+        <v>9494.33594956889</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.0000749809738003076</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.00654778337064408</v>
+      </c>
+      <c r="K68" t="n">
+        <v>5223.83777701436</v>
+      </c>
+      <c r="L68"/>
+      <c r="M68"/>
+      <c r="N68"/>
+      <c r="O68"/>
+      <c r="P68"/>
+      <c r="Q68"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" t="s">
+        <v>18</v>
+      </c>
+      <c r="C69" t="s">
+        <v>20</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" t="n">
+        <v>-6.51710298192551</v>
+      </c>
+      <c r="G69" t="n">
+        <v>-6.52934045014372</v>
+      </c>
+      <c r="H69" t="n">
+        <v>9584.54244036084</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.0000749853401013443</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.00654991861742095</v>
+      </c>
+      <c r="K69" t="n">
+        <v>5225.20158469222</v>
+      </c>
+      <c r="L69"/>
+      <c r="M69"/>
+      <c r="N69"/>
+      <c r="O69"/>
+      <c r="P69"/>
+      <c r="Q69"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" t="s">
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>19</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" t="n">
+        <v>-6.46720979550528</v>
+      </c>
+      <c r="G70" t="n">
+        <v>-6.47740768568712</v>
+      </c>
+      <c r="H70" t="n">
+        <v>9507.357074903</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.0000750090434852183</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.00655431788345669</v>
+      </c>
+      <c r="K70" t="n">
+        <v>5228.17585912406</v>
+      </c>
+      <c r="L70"/>
+      <c r="M70"/>
+      <c r="N70"/>
+      <c r="O70"/>
+      <c r="P70"/>
+      <c r="Q70"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>33</v>
+      </c>
+      <c r="B71" t="s">
+        <v>21</v>
+      </c>
+      <c r="C71" t="s">
+        <v>20</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>-6.5196466272262</v>
+      </c>
+      <c r="G71" t="n">
+        <v>-6.53392367348077</v>
+      </c>
+      <c r="H71" t="n">
+        <v>9592.26602899629</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.0000750206224158353</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.00655589262678087</v>
+      </c>
+      <c r="K71" t="n">
+        <v>5249.68246429117</v>
+      </c>
+      <c r="L71"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="P71"/>
+      <c r="Q71"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>33</v>
+      </c>
+      <c r="B72" t="s">
+        <v>22</v>
+      </c>
+      <c r="C72" t="s">
+        <v>19</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" t="n">
+        <v>-6.46400431428354</v>
+      </c>
+      <c r="G72" t="n">
+        <v>-6.47420220446538</v>
+      </c>
+      <c r="H72" t="n">
+        <v>9502.65463395071</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.000075001729664675</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.0065531799888595</v>
+      </c>
+      <c r="K72" t="n">
+        <v>5239.7572907379</v>
+      </c>
+      <c r="L72"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="P72"/>
+      <c r="Q72"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>33</v>
+      </c>
+      <c r="B73" t="s">
+        <v>22</v>
+      </c>
+      <c r="C73" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" t="n">
+        <v>-6.51832153330266</v>
+      </c>
+      <c r="G73" t="n">
+        <v>-6.53259857955724</v>
+      </c>
+      <c r="H73" t="n">
+        <v>9590.32211621047</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.0000750063614617873</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.00655391108609953</v>
+      </c>
+      <c r="K73" t="n">
+        <v>5250.7919215142</v>
+      </c>
+      <c r="L73"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="P73"/>
+      <c r="Q73"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/outputs/robust_garch_order/garch_order_robustness_results.xlsx
+++ b/outputs/robust_garch_order/garch_order_robustness_results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">asset</t>
   </si>
@@ -86,15 +86,6 @@
     <t xml:space="preserve">MSFT</t>
   </si>
   <si>
-    <t xml:space="preserve">PG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WMT</t>
-  </si>
-  <si>
     <t xml:space="preserve">AMZN</t>
   </si>
   <si>
@@ -104,16 +95,7 @@
     <t xml:space="preserve">GBPUSD</t>
   </si>
   <si>
-    <t xml:space="preserve">GBPCNY</t>
-  </si>
-  <si>
     <t xml:space="preserve">USDZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GBPZAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EURZAR</t>
   </si>
 </sst>
 </file>
@@ -1001,25 +983,25 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.39182107974727</v>
+        <v>-4.60414114225732</v>
       </c>
       <c r="G14" t="n">
-        <v>-6.39997939189274</v>
+        <v>-4.61433903243915</v>
       </c>
       <c r="H14" t="n">
-        <v>9392.76976790665</v>
+        <v>6774.23536058824</v>
       </c>
       <c r="I14" t="n">
-        <v>0.000173027768537589</v>
+        <v>0.000497740511723748</v>
       </c>
       <c r="J14" t="n">
-        <v>0.00873820806998403</v>
+        <v>0.0158454868126219</v>
       </c>
       <c r="K14" t="n">
-        <v>4511.97269537235</v>
+        <v>3775.86640303834</v>
       </c>
       <c r="L14"/>
       <c r="M14"/>
@@ -1045,22 +1027,22 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.52162145575324</v>
+        <v>-4.92230222145556</v>
       </c>
       <c r="G15" t="n">
-        <v>-6.53385892397145</v>
+        <v>-4.93453968967376</v>
       </c>
       <c r="H15" t="n">
-        <v>9591.17104146612</v>
+        <v>7244.96972475141</v>
       </c>
       <c r="I15" t="n">
-        <v>0.000173039430930777</v>
+        <v>0.000497770066310838</v>
       </c>
       <c r="J15" t="n">
-        <v>0.00874119201201824</v>
+        <v>0.0158455186507115</v>
       </c>
       <c r="K15" t="n">
-        <v>4599.25542302957</v>
+        <v>3770.36100626239</v>
       </c>
       <c r="L15"/>
       <c r="M15"/>
@@ -1080,28 +1062,28 @@
         <v>19</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.40127332888572</v>
+        <v>-4.66126790841841</v>
       </c>
       <c r="G16" t="n">
-        <v>-6.41147121906755</v>
+        <v>-4.67554495467298</v>
       </c>
       <c r="H16" t="n">
-        <v>9410.6282783721</v>
+        <v>6866.02444850527</v>
       </c>
       <c r="I16" t="n">
-        <v>0.000173101279562829</v>
+        <v>0.00049739528381817</v>
       </c>
       <c r="J16" t="n">
-        <v>0.00875102013775755</v>
+        <v>0.0158657957046253</v>
       </c>
       <c r="K16" t="n">
-        <v>4579.15323567698</v>
+        <v>3408.00015714302</v>
       </c>
       <c r="L16"/>
       <c r="M16"/>
@@ -1127,22 +1109,22 @@
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.5319140533739</v>
+        <v>-4.94604003763756</v>
       </c>
       <c r="G17" t="n">
-        <v>-6.54619109962847</v>
+        <v>-4.96031708389214</v>
       </c>
       <c r="H17" t="n">
-        <v>9610.26234315497</v>
+        <v>7283.78516206976</v>
       </c>
       <c r="I17" t="n">
-        <v>0.000173101265083896</v>
+        <v>0.000497547922696646</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00875101830170995</v>
+        <v>0.0158462434773637</v>
       </c>
       <c r="K17" t="n">
-        <v>4438.27689190541</v>
+        <v>3755.12028192146</v>
       </c>
       <c r="L17"/>
       <c r="M17"/>
@@ -1162,28 +1144,28 @@
         <v>19</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.39488808544956</v>
+        <v>-4.61564666631265</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.4050859756314</v>
+        <v>-4.62992371256722</v>
       </c>
       <c r="H18" t="n">
-        <v>9401.26112625126</v>
+        <v>6799.09808633611</v>
       </c>
       <c r="I18" t="n">
-        <v>0.000173078430269965</v>
+        <v>0.00049773766393544</v>
       </c>
       <c r="J18" t="n">
-        <v>0.00874793998571388</v>
+        <v>0.0158454882074985</v>
       </c>
       <c r="K18" t="n">
-        <v>4473.98355355345</v>
+        <v>3772.44626204037</v>
       </c>
       <c r="L18"/>
       <c r="M18"/>
@@ -1209,22 +1191,22 @@
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.52439191144956</v>
+        <v>-4.92784796932361</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.53866895770414</v>
+        <v>-4.94212501557818</v>
       </c>
       <c r="H19" t="n">
-        <v>9599.22736095197</v>
+        <v>7257.09739785319</v>
       </c>
       <c r="I19" t="n">
-        <v>0.000173075547909668</v>
+        <v>0.000497658267645776</v>
       </c>
       <c r="J19" t="n">
-        <v>0.00874751947582641</v>
+        <v>0.0158456243308415</v>
       </c>
       <c r="K19" t="n">
-        <v>4589.33776613516</v>
+        <v>3655.22998537484</v>
       </c>
       <c r="L19"/>
       <c r="M19"/>
@@ -1250,22 +1232,22 @@
         <v>1</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.16357918424433</v>
+        <v>-7.40778478998216</v>
       </c>
       <c r="G20" t="n">
-        <v>-5.1717374963898</v>
+        <v>-7.41594310212763</v>
       </c>
       <c r="H20" t="n">
-        <v>7590.93890720383</v>
+        <v>10883.1885308212</v>
       </c>
       <c r="I20" t="n">
-        <v>0.000427009808579778</v>
+        <v>0.0000220871377796025</v>
       </c>
       <c r="J20" t="n">
-        <v>0.0148885450504351</v>
+        <v>0.00350164710606259</v>
       </c>
       <c r="K20" t="n">
-        <v>3880.57558501832</v>
+        <v>6117.39575516507</v>
       </c>
       <c r="L20"/>
       <c r="M20"/>
@@ -1291,22 +1273,22 @@
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.26867524332051</v>
+        <v>-7.45675061975955</v>
       </c>
       <c r="G21" t="n">
-        <v>-5.28091271153872</v>
+        <v>-7.46898808797776</v>
       </c>
       <c r="H21" t="n">
-        <v>7753.0989478273</v>
+        <v>10963.0055250634</v>
       </c>
       <c r="I21" t="n">
-        <v>0.000427009099004181</v>
+        <v>0.0000220825179097488</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0148885873227819</v>
+        <v>0.00350114827143889</v>
       </c>
       <c r="K21" t="n">
-        <v>3860.22807488225</v>
+        <v>6043.9607137356</v>
       </c>
       <c r="L21"/>
       <c r="M21"/>
@@ -1326,28 +1308,28 @@
         <v>19</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.19669226616628</v>
+        <v>-7.40495350240917</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.20689015634812</v>
+        <v>-7.41923054866374</v>
       </c>
       <c r="H22" t="n">
-        <v>7643.50785936269</v>
+        <v>10891.0112148897</v>
       </c>
       <c r="I22" t="n">
-        <v>0.000427041701878454</v>
+        <v>0.0000220810159775232</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0148944310725243</v>
+        <v>0.00350093835243901</v>
       </c>
       <c r="K22" t="n">
-        <v>3872.41989278354</v>
+        <v>5981.44223636607</v>
       </c>
       <c r="L22"/>
       <c r="M22"/>
@@ -1373,22 +1355,22 @@
         <v>1</v>
       </c>
       <c r="F23" t="n">
-        <v>-5.29241997443249</v>
+        <v>-7.45625481489064</v>
       </c>
       <c r="G23" t="n">
-        <v>-5.30669702068706</v>
+        <v>-7.47053186114522</v>
       </c>
       <c r="H23" t="n">
-        <v>7791.92452934792</v>
+        <v>10966.2702403</v>
       </c>
       <c r="I23" t="n">
-        <v>0.000427013408151869</v>
+        <v>0.0000220789981361393</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0148922032540321</v>
+        <v>0.00350061520003008</v>
       </c>
       <c r="K23" t="n">
-        <v>3745.30658587702</v>
+        <v>6153.91647861519</v>
       </c>
       <c r="L23"/>
       <c r="M23"/>
@@ -1414,22 +1396,22 @@
         <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.17318773502243</v>
+        <v>-7.40580510083685</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.18338562520427</v>
+        <v>-7.41600299101869</v>
       </c>
       <c r="H24" t="n">
-        <v>7609.02671217467</v>
+        <v>10884.2763878244</v>
       </c>
       <c r="I24" t="n">
-        <v>0.000427001068326632</v>
+        <v>0.0000220841774675933</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0148904087713498</v>
+        <v>0.00350134658975511</v>
       </c>
       <c r="K24" t="n">
-        <v>3853.70930192326</v>
+        <v>6112.72531273013</v>
       </c>
       <c r="L24"/>
       <c r="M24"/>
@@ -1455,22 +1437,22 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.27568743839133</v>
+        <v>-7.45419380852886</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.28996448464591</v>
+        <v>-7.46847085478344</v>
       </c>
       <c r="H25" t="n">
-        <v>7767.37789897555</v>
+        <v>10963.2467439673</v>
       </c>
       <c r="I25" t="n">
-        <v>0.000427002105418983</v>
+        <v>0.0000220813043327487</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0148906642105145</v>
+        <v>0.00350098165160568</v>
       </c>
       <c r="K25" t="n">
-        <v>3885.3361056724</v>
+        <v>6063.57101232905</v>
       </c>
       <c r="L25"/>
       <c r="M25"/>
@@ -1496,22 +1478,22 @@
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.08014781948621</v>
+        <v>-7.47350817319533</v>
       </c>
       <c r="G26" t="n">
-        <v>-6.08830613163168</v>
+        <v>-7.4816664853408</v>
       </c>
       <c r="H26" t="n">
-        <v>8935.54509510367</v>
+        <v>10979.604733995</v>
       </c>
       <c r="I26" t="n">
-        <v>0.000203936033515385</v>
+        <v>0.0000343215151853892</v>
       </c>
       <c r="J26" t="n">
-        <v>0.00920850200164572</v>
+        <v>0.00431188888545906</v>
       </c>
       <c r="K26" t="n">
-        <v>4453.71610324234</v>
+        <v>5850.6497879914</v>
       </c>
       <c r="L26"/>
       <c r="M26"/>
@@ -1537,22 +1519,22 @@
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.22168721079134</v>
+        <v>-7.52948011214007</v>
       </c>
       <c r="G27" t="n">
-        <v>-6.23392467900954</v>
+        <v>-7.54171758035828</v>
       </c>
       <c r="H27" t="n">
-        <v>9151.167504107</v>
+        <v>11069.6996903856</v>
       </c>
       <c r="I27" t="n">
-        <v>0.000203930400296643</v>
+        <v>0.0000343216848446396</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0092081932084695</v>
+        <v>0.00431165913418082</v>
       </c>
       <c r="K27" t="n">
-        <v>4452.99738386152</v>
+        <v>5884.64928742832</v>
       </c>
       <c r="L27"/>
       <c r="M27"/>
@@ -1578,22 +1560,22 @@
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.08805526132953</v>
+        <v>-7.47562123655602</v>
       </c>
       <c r="G28" t="n">
-        <v>-6.1023323075841</v>
+        <v>-7.4898982828106</v>
       </c>
       <c r="H28" t="n">
-        <v>8959.12149522587</v>
+        <v>10994.6807808831</v>
       </c>
       <c r="I28" t="n">
-        <v>0.000203988863102013</v>
+        <v>0.0000343228481663364</v>
       </c>
       <c r="J28" t="n">
-        <v>0.00921094882594286</v>
+        <v>0.00431286081058617</v>
       </c>
       <c r="K28" t="n">
-        <v>4460.64205783928</v>
+        <v>5806.24216921478</v>
       </c>
       <c r="L28"/>
       <c r="M28"/>
@@ -1619,22 +1601,22 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.23014234000606</v>
+        <v>-7.53495360155169</v>
       </c>
       <c r="G29" t="n">
-        <v>-6.24441938626063</v>
+        <v>-7.54923064780626</v>
       </c>
       <c r="H29" t="n">
-        <v>9167.56323964435</v>
+        <v>11081.7213603318</v>
       </c>
       <c r="I29" t="n">
-        <v>0.000203962093851359</v>
+        <v>0.0000343230886993207</v>
       </c>
       <c r="J29" t="n">
-        <v>0.00920976802727746</v>
+        <v>0.00431295439035695</v>
       </c>
       <c r="K29" t="n">
-        <v>4378.96069234667</v>
+        <v>5868.82638053184</v>
       </c>
       <c r="L29"/>
       <c r="M29"/>
@@ -1654,28 +1636,28 @@
         <v>19</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>-6.08126240318086</v>
+        <v>-7.47078512447476</v>
       </c>
       <c r="G30" t="n">
-        <v>-6.09553944943544</v>
+        <v>-7.4809830146566</v>
       </c>
       <c r="H30" t="n">
-        <v>8949.15637232179</v>
+        <v>10979.6020825012</v>
       </c>
       <c r="I30" t="n">
-        <v>0.000203962122638318</v>
+        <v>0.0000343215135640158</v>
       </c>
       <c r="J30" t="n">
-        <v>0.00920976930847519</v>
+        <v>0.00431189520008064</v>
       </c>
       <c r="K30" t="n">
-        <v>4452.28198275149</v>
+        <v>5849.22822585094</v>
       </c>
       <c r="L30"/>
       <c r="M30"/>
@@ -1701,22 +1683,22 @@
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>-6.22092445790455</v>
+        <v>-7.5269216122679</v>
       </c>
       <c r="G31" t="n">
-        <v>-6.23520150415912</v>
+        <v>-7.54119865852247</v>
       </c>
       <c r="H31" t="n">
-        <v>9154.04060660143</v>
+        <v>11069.9384320525</v>
       </c>
       <c r="I31" t="n">
-        <v>0.000203955604340564</v>
+        <v>0.0000343218278717042</v>
       </c>
       <c r="J31" t="n">
-        <v>0.00920947343569041</v>
+        <v>0.00431156206233229</v>
       </c>
       <c r="K31" t="n">
-        <v>4441.35175990047</v>
+        <v>5884.56321600794</v>
       </c>
       <c r="L31"/>
       <c r="M31"/>
@@ -1739,25 +1721,25 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.60414114225732</v>
+        <v>-6.27551453014706</v>
       </c>
       <c r="G32" t="n">
-        <v>-4.61433903243915</v>
+        <v>-6.28367284229253</v>
       </c>
       <c r="H32" t="n">
-        <v>6774.23536058824</v>
+        <v>9222.14805964314</v>
       </c>
       <c r="I32" t="n">
-        <v>0.000497740511723748</v>
+        <v>0.0000979522875034966</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0158454868126219</v>
+        <v>0.00762067318767246</v>
       </c>
       <c r="K32" t="n">
-        <v>3775.86640303834</v>
+        <v>5029.22619018546</v>
       </c>
       <c r="L32"/>
       <c r="M32"/>
@@ -1783,22 +1765,22 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.92230222145556</v>
+        <v>-6.30779688142885</v>
       </c>
       <c r="G33" t="n">
-        <v>-4.93453968967376</v>
+        <v>-6.32003434964706</v>
       </c>
       <c r="H33" t="n">
-        <v>7244.96972475141</v>
+        <v>9277.49039093223</v>
       </c>
       <c r="I33" t="n">
-        <v>0.000497770066310838</v>
+        <v>0.0000979513859633547</v>
       </c>
       <c r="J33" t="n">
-        <v>0.0158455186507115</v>
+        <v>0.00762025430347554</v>
       </c>
       <c r="K33" t="n">
-        <v>3770.36100626239</v>
+        <v>5035.98410313405</v>
       </c>
       <c r="L33"/>
       <c r="M33"/>
@@ -1821,25 +1803,25 @@
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.66126790841841</v>
+        <v>-6.27772262421088</v>
       </c>
       <c r="G34" t="n">
-        <v>-4.67554495467298</v>
+        <v>-6.29403924850182</v>
       </c>
       <c r="H34" t="n">
-        <v>6866.02444850527</v>
+        <v>9241.35557755217</v>
       </c>
       <c r="I34" t="n">
-        <v>0.00049739528381817</v>
+        <v>0.0000980106546343087</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0158657957046253</v>
+        <v>0.00763212416347733</v>
       </c>
       <c r="K34" t="n">
-        <v>3408.00015714302</v>
+        <v>5038.02723708611</v>
       </c>
       <c r="L34"/>
       <c r="M34"/>
@@ -1865,22 +1847,22 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>-4.94604003763756</v>
+        <v>-6.3083005107007</v>
       </c>
       <c r="G35" t="n">
-        <v>-4.96031708389214</v>
+        <v>-6.32257755695527</v>
       </c>
       <c r="H35" t="n">
-        <v>7283.78516206976</v>
+        <v>9282.22127605338</v>
       </c>
       <c r="I35" t="n">
-        <v>0.000497547922696646</v>
+        <v>0.0000979932584494563</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0158462434773637</v>
+        <v>0.00762968525547159</v>
       </c>
       <c r="K35" t="n">
-        <v>3755.12028192146</v>
+        <v>5049.20315589203</v>
       </c>
       <c r="L35"/>
       <c r="M35"/>
@@ -1900,28 +1882,28 @@
         <v>19</v>
       </c>
       <c r="D36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>-4.61564666631265</v>
+        <v>-6.27645225149923</v>
       </c>
       <c r="G36" t="n">
-        <v>-4.62992371256722</v>
+        <v>-6.28665014168107</v>
       </c>
       <c r="H36" t="n">
-        <v>6799.09808633611</v>
+        <v>9227.51575784613</v>
       </c>
       <c r="I36" t="n">
-        <v>0.00049773766393544</v>
+        <v>0.0000979829340566733</v>
       </c>
       <c r="J36" t="n">
-        <v>0.0158454882074985</v>
+        <v>0.00762808126779227</v>
       </c>
       <c r="K36" t="n">
-        <v>3772.44626204037</v>
+        <v>5044.08121193212</v>
       </c>
       <c r="L36"/>
       <c r="M36"/>
@@ -1947,22 +1929,22 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>-4.92784796932361</v>
+        <v>-6.30940745543358</v>
       </c>
       <c r="G37" t="n">
-        <v>-4.94212501557818</v>
+        <v>-6.32368450168815</v>
       </c>
       <c r="H37" t="n">
-        <v>7257.09739785319</v>
+        <v>9283.84516397652</v>
       </c>
       <c r="I37" t="n">
-        <v>0.000497658267645776</v>
+        <v>0.0000979822741112018</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0158456243308415</v>
+        <v>0.00762797192350798</v>
       </c>
       <c r="K37" t="n">
-        <v>3655.22998537484</v>
+        <v>5051.80195164274</v>
       </c>
       <c r="L37"/>
       <c r="M37"/>
@@ -1971,1482 +1953,6 @@
       <c r="P37"/>
       <c r="Q37"/>
     </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" t="s">
-        <v>18</v>
-      </c>
-      <c r="C38" t="s">
-        <v>19</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
-        <v>-7.40778478998216</v>
-      </c>
-      <c r="G38" t="n">
-        <v>-7.41594310212763</v>
-      </c>
-      <c r="H38" t="n">
-        <v>10883.1885308212</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.0000220871377796025</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.00350164710606259</v>
-      </c>
-      <c r="K38" t="n">
-        <v>6117.39575516507</v>
-      </c>
-      <c r="L38"/>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
-      <c r="P38"/>
-      <c r="Q38"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B39" t="s">
-        <v>18</v>
-      </c>
-      <c r="C39" t="s">
-        <v>20</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-7.45675061975955</v>
-      </c>
-      <c r="G39" t="n">
-        <v>-7.46898808797776</v>
-      </c>
-      <c r="H39" t="n">
-        <v>10963.0055250634</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.0000220825179097488</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.00350114827143889</v>
-      </c>
-      <c r="K39" t="n">
-        <v>6043.9607137356</v>
-      </c>
-      <c r="L39"/>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
-      <c r="P39"/>
-      <c r="Q39"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>28</v>
-      </c>
-      <c r="B40" t="s">
-        <v>21</v>
-      </c>
-      <c r="C40" t="s">
-        <v>19</v>
-      </c>
-      <c r="D40" t="n">
-        <v>2</v>
-      </c>
-      <c r="E40" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" t="n">
-        <v>-7.40495350240917</v>
-      </c>
-      <c r="G40" t="n">
-        <v>-7.41923054866374</v>
-      </c>
-      <c r="H40" t="n">
-        <v>10891.0112148897</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.0000220810159775232</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.00350093835243901</v>
-      </c>
-      <c r="K40" t="n">
-        <v>5981.44223636607</v>
-      </c>
-      <c r="L40"/>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-      <c r="P40"/>
-      <c r="Q40"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>28</v>
-      </c>
-      <c r="B41" t="s">
-        <v>21</v>
-      </c>
-      <c r="C41" t="s">
-        <v>20</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-7.45625481489064</v>
-      </c>
-      <c r="G41" t="n">
-        <v>-7.47053186114522</v>
-      </c>
-      <c r="H41" t="n">
-        <v>10966.2702403</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.0000220789981361393</v>
-      </c>
-      <c r="J41" t="n">
-        <v>0.00350061520003008</v>
-      </c>
-      <c r="K41" t="n">
-        <v>6153.91647861519</v>
-      </c>
-      <c r="L41"/>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41"/>
-      <c r="P41"/>
-      <c r="Q41"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>28</v>
-      </c>
-      <c r="B42" t="s">
-        <v>22</v>
-      </c>
-      <c r="C42" t="s">
-        <v>19</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" t="n">
-        <v>-7.40580510083685</v>
-      </c>
-      <c r="G42" t="n">
-        <v>-7.41600299101869</v>
-      </c>
-      <c r="H42" t="n">
-        <v>10884.2763878244</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0.0000220841774675933</v>
-      </c>
-      <c r="J42" t="n">
-        <v>0.00350134658975511</v>
-      </c>
-      <c r="K42" t="n">
-        <v>6112.72531273013</v>
-      </c>
-      <c r="L42"/>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-      <c r="P42"/>
-      <c r="Q42"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B43" t="s">
-        <v>22</v>
-      </c>
-      <c r="C43" t="s">
-        <v>20</v>
-      </c>
-      <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="n">
-        <v>-7.45419380852886</v>
-      </c>
-      <c r="G43" t="n">
-        <v>-7.46847085478344</v>
-      </c>
-      <c r="H43" t="n">
-        <v>10963.2467439673</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0.0000220813043327487</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0.00350098165160568</v>
-      </c>
-      <c r="K43" t="n">
-        <v>6063.57101232905</v>
-      </c>
-      <c r="L43"/>
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
-      <c r="P43"/>
-      <c r="Q43"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>29</v>
-      </c>
-      <c r="B44" t="s">
-        <v>18</v>
-      </c>
-      <c r="C44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-7.47350817319533</v>
-      </c>
-      <c r="G44" t="n">
-        <v>-7.4816664853408</v>
-      </c>
-      <c r="H44" t="n">
-        <v>10979.604733995</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0.0000343215151853892</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0.00431188888545906</v>
-      </c>
-      <c r="K44" t="n">
-        <v>5850.6497879914</v>
-      </c>
-      <c r="L44"/>
-      <c r="M44"/>
-      <c r="N44"/>
-      <c r="O44"/>
-      <c r="P44"/>
-      <c r="Q44"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>29</v>
-      </c>
-      <c r="B45" t="s">
-        <v>18</v>
-      </c>
-      <c r="C45" t="s">
-        <v>20</v>
-      </c>
-      <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" t="n">
-        <v>-7.52948011214007</v>
-      </c>
-      <c r="G45" t="n">
-        <v>-7.54171758035828</v>
-      </c>
-      <c r="H45" t="n">
-        <v>11069.6996903856</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.0000343216848446396</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0.00431165913418082</v>
-      </c>
-      <c r="K45" t="n">
-        <v>5884.64928742832</v>
-      </c>
-      <c r="L45"/>
-      <c r="M45"/>
-      <c r="N45"/>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>29</v>
-      </c>
-      <c r="B46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" t="n">
-        <v>-7.47562123655602</v>
-      </c>
-      <c r="G46" t="n">
-        <v>-7.4898982828106</v>
-      </c>
-      <c r="H46" t="n">
-        <v>10994.6807808831</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.0000343228481663364</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.00431286081058617</v>
-      </c>
-      <c r="K46" t="n">
-        <v>5806.24216921478</v>
-      </c>
-      <c r="L46"/>
-      <c r="M46"/>
-      <c r="N46"/>
-      <c r="O46"/>
-      <c r="P46"/>
-      <c r="Q46"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>29</v>
-      </c>
-      <c r="B47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47" t="s">
-        <v>20</v>
-      </c>
-      <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" t="n">
-        <v>-7.53495360155169</v>
-      </c>
-      <c r="G47" t="n">
-        <v>-7.54923064780626</v>
-      </c>
-      <c r="H47" t="n">
-        <v>11081.7213603318</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.0000343230886993207</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0.00431295439035695</v>
-      </c>
-      <c r="K47" t="n">
-        <v>5868.82638053184</v>
-      </c>
-      <c r="L47"/>
-      <c r="M47"/>
-      <c r="N47"/>
-      <c r="O47"/>
-      <c r="P47"/>
-      <c r="Q47"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>29</v>
-      </c>
-      <c r="B48" t="s">
-        <v>22</v>
-      </c>
-      <c r="C48" t="s">
-        <v>19</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" t="n">
-        <v>-7.47078512447476</v>
-      </c>
-      <c r="G48" t="n">
-        <v>-7.4809830146566</v>
-      </c>
-      <c r="H48" t="n">
-        <v>10979.6020825012</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0.0000343215135640158</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.00431189520008064</v>
-      </c>
-      <c r="K48" t="n">
-        <v>5849.22822585094</v>
-      </c>
-      <c r="L48"/>
-      <c r="M48"/>
-      <c r="N48"/>
-      <c r="O48"/>
-      <c r="P48"/>
-      <c r="Q48"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>29</v>
-      </c>
-      <c r="B49" t="s">
-        <v>22</v>
-      </c>
-      <c r="C49" t="s">
-        <v>20</v>
-      </c>
-      <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-7.5269216122679</v>
-      </c>
-      <c r="G49" t="n">
-        <v>-7.54119865852247</v>
-      </c>
-      <c r="H49" t="n">
-        <v>11069.9384320525</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.0000343218278717042</v>
-      </c>
-      <c r="J49" t="n">
-        <v>0.00431156206233229</v>
-      </c>
-      <c r="K49" t="n">
-        <v>5884.56321600794</v>
-      </c>
-      <c r="L49"/>
-      <c r="M49"/>
-      <c r="N49"/>
-      <c r="O49"/>
-      <c r="P49"/>
-      <c r="Q49"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>30</v>
-      </c>
-      <c r="B50" t="s">
-        <v>18</v>
-      </c>
-      <c r="C50" t="s">
-        <v>19</v>
-      </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="n">
-        <v>1</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-7.44504153616433</v>
-      </c>
-      <c r="G50" t="n">
-        <v>-7.4531998483098</v>
-      </c>
-      <c r="H50" t="n">
-        <v>10937.8441774705</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.000030470814016406</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0.00408182322711205</v>
-      </c>
-      <c r="K50" t="n">
-        <v>5837.19208338236</v>
-      </c>
-      <c r="L50"/>
-      <c r="M50"/>
-      <c r="N50"/>
-      <c r="O50"/>
-      <c r="P50"/>
-      <c r="Q50"/>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>30</v>
-      </c>
-      <c r="B51" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" t="s">
-        <v>20</v>
-      </c>
-      <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="n">
-        <v>1</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-7.49221066754127</v>
-      </c>
-      <c r="G51" t="n">
-        <v>-7.50444813575948</v>
-      </c>
-      <c r="H51" t="n">
-        <v>11015.0254151592</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.0000304678767962828</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0.00408109018837926</v>
-      </c>
-      <c r="K51" t="n">
-        <v>5958.25992226711</v>
-      </c>
-      <c r="L51"/>
-      <c r="M51"/>
-      <c r="N51"/>
-      <c r="O51"/>
-      <c r="P51"/>
-      <c r="Q51"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B52" t="s">
-        <v>21</v>
-      </c>
-      <c r="C52" t="s">
-        <v>19</v>
-      </c>
-      <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-7.44211154699923</v>
-      </c>
-      <c r="G52" t="n">
-        <v>-7.45230943718107</v>
-      </c>
-      <c r="H52" t="n">
-        <v>10937.5379443446</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.0000304857968667413</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0.00408488160823153</v>
-      </c>
-      <c r="K52" t="n">
-        <v>5780.83066380907</v>
-      </c>
-      <c r="L52"/>
-      <c r="M52"/>
-      <c r="N52"/>
-      <c r="O52"/>
-      <c r="P52"/>
-      <c r="Q52"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>30</v>
-      </c>
-      <c r="B53" t="s">
-        <v>21</v>
-      </c>
-      <c r="C53" t="s">
-        <v>20</v>
-      </c>
-      <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-7.49888455121143</v>
-      </c>
-      <c r="G53" t="n">
-        <v>-7.51316159746601</v>
-      </c>
-      <c r="H53" t="n">
-        <v>11028.8080634826</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.0000304953170051174</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0.00408651669944771</v>
-      </c>
-      <c r="K53" t="n">
-        <v>5977.6734536854</v>
-      </c>
-      <c r="L53"/>
-      <c r="M53"/>
-      <c r="N53"/>
-      <c r="O53"/>
-      <c r="P53"/>
-      <c r="Q53"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>30</v>
-      </c>
-      <c r="B54" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" t="s">
-        <v>19</v>
-      </c>
-      <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-7.44256812678184</v>
-      </c>
-      <c r="G54" t="n">
-        <v>-7.45276601696368</v>
-      </c>
-      <c r="H54" t="n">
-        <v>10938.2077468857</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0.0000304735409074575</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.00408245461970814</v>
-      </c>
-      <c r="K54" t="n">
-        <v>5854.04064867584</v>
-      </c>
-      <c r="L54"/>
-      <c r="M54"/>
-      <c r="N54"/>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" t="s">
-        <v>20</v>
-      </c>
-      <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-7.49257558127722</v>
-      </c>
-      <c r="G55" t="n">
-        <v>-7.5068526275318</v>
-      </c>
-      <c r="H55" t="n">
-        <v>11019.5528045891</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0.0000304734809874528</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.00408244119127097</v>
-      </c>
-      <c r="K55" t="n">
-        <v>5976.66516051836</v>
-      </c>
-      <c r="L55"/>
-      <c r="M55"/>
-      <c r="N55"/>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>31</v>
-      </c>
-      <c r="B56" t="s">
-        <v>18</v>
-      </c>
-      <c r="C56" t="s">
-        <v>19</v>
-      </c>
-      <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-6.27551453014706</v>
-      </c>
-      <c r="G56" t="n">
-        <v>-6.28367284229253</v>
-      </c>
-      <c r="H56" t="n">
-        <v>9222.14805964314</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0.0000979522875034966</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.00762067318767246</v>
-      </c>
-      <c r="K56" t="n">
-        <v>5029.22619018546</v>
-      </c>
-      <c r="L56"/>
-      <c r="M56"/>
-      <c r="N56"/>
-      <c r="O56"/>
-      <c r="P56"/>
-      <c r="Q56"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>31</v>
-      </c>
-      <c r="B57" t="s">
-        <v>18</v>
-      </c>
-      <c r="C57" t="s">
-        <v>20</v>
-      </c>
-      <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-6.30779688142885</v>
-      </c>
-      <c r="G57" t="n">
-        <v>-6.32003434964706</v>
-      </c>
-      <c r="H57" t="n">
-        <v>9277.49039093223</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0.0000979513859633547</v>
-      </c>
-      <c r="J57" t="n">
-        <v>0.00762025430347554</v>
-      </c>
-      <c r="K57" t="n">
-        <v>5035.98410313405</v>
-      </c>
-      <c r="L57"/>
-      <c r="M57"/>
-      <c r="N57"/>
-      <c r="O57"/>
-      <c r="P57"/>
-      <c r="Q57"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>31</v>
-      </c>
-      <c r="B58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C58" t="s">
-        <v>19</v>
-      </c>
-      <c r="D58" t="n">
-        <v>2</v>
-      </c>
-      <c r="E58" t="n">
-        <v>2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-6.27772262421088</v>
-      </c>
-      <c r="G58" t="n">
-        <v>-6.29403924850182</v>
-      </c>
-      <c r="H58" t="n">
-        <v>9241.35557755217</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0.0000980106546343087</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.00763212416347733</v>
-      </c>
-      <c r="K58" t="n">
-        <v>5038.02723708611</v>
-      </c>
-      <c r="L58"/>
-      <c r="M58"/>
-      <c r="N58"/>
-      <c r="O58"/>
-      <c r="P58"/>
-      <c r="Q58"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>31</v>
-      </c>
-      <c r="B59" t="s">
-        <v>21</v>
-      </c>
-      <c r="C59" t="s">
-        <v>20</v>
-      </c>
-      <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-6.3083005107007</v>
-      </c>
-      <c r="G59" t="n">
-        <v>-6.32257755695527</v>
-      </c>
-      <c r="H59" t="n">
-        <v>9282.22127605338</v>
-      </c>
-      <c r="I59" t="n">
-        <v>0.0000979932584494563</v>
-      </c>
-      <c r="J59" t="n">
-        <v>0.00762968525547159</v>
-      </c>
-      <c r="K59" t="n">
-        <v>5049.20315589203</v>
-      </c>
-      <c r="L59"/>
-      <c r="M59"/>
-      <c r="N59"/>
-      <c r="O59"/>
-      <c r="P59"/>
-      <c r="Q59"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>31</v>
-      </c>
-      <c r="B60" t="s">
-        <v>22</v>
-      </c>
-      <c r="C60" t="s">
-        <v>19</v>
-      </c>
-      <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="n">
-        <v>1</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-6.27645225149923</v>
-      </c>
-      <c r="G60" t="n">
-        <v>-6.28665014168107</v>
-      </c>
-      <c r="H60" t="n">
-        <v>9227.51575784613</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.0000979829340566733</v>
-      </c>
-      <c r="J60" t="n">
-        <v>0.00762808126779227</v>
-      </c>
-      <c r="K60" t="n">
-        <v>5044.08121193212</v>
-      </c>
-      <c r="L60"/>
-      <c r="M60"/>
-      <c r="N60"/>
-      <c r="O60"/>
-      <c r="P60"/>
-      <c r="Q60"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>31</v>
-      </c>
-      <c r="B61" t="s">
-        <v>22</v>
-      </c>
-      <c r="C61" t="s">
-        <v>20</v>
-      </c>
-      <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="n">
-        <v>1</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-6.30940745543358</v>
-      </c>
-      <c r="G61" t="n">
-        <v>-6.32368450168815</v>
-      </c>
-      <c r="H61" t="n">
-        <v>9283.84516397652</v>
-      </c>
-      <c r="I61" t="n">
-        <v>0.0000979822741112018</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.00762797192350798</v>
-      </c>
-      <c r="K61" t="n">
-        <v>5051.80195164274</v>
-      </c>
-      <c r="L61"/>
-      <c r="M61"/>
-      <c r="N61"/>
-      <c r="O61"/>
-      <c r="P61"/>
-      <c r="Q61"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>32</v>
-      </c>
-      <c r="B62" t="s">
-        <v>18</v>
-      </c>
-      <c r="C62" t="s">
-        <v>19</v>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-6.4297097377123</v>
-      </c>
-      <c r="G62" t="n">
-        <v>-6.43786804985777</v>
-      </c>
-      <c r="H62" t="n">
-        <v>9448.35242914135</v>
-      </c>
-      <c r="I62" t="n">
-        <v>0.0000803339350240065</v>
-      </c>
-      <c r="J62" t="n">
-        <v>0.00675909651890509</v>
-      </c>
-      <c r="K62" t="n">
-        <v>5177.3961190569</v>
-      </c>
-      <c r="L62"/>
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="O62"/>
-      <c r="P62"/>
-      <c r="Q62"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>32</v>
-      </c>
-      <c r="B63" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" t="s">
-        <v>20</v>
-      </c>
-      <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-6.47125091630012</v>
-      </c>
-      <c r="G63" t="n">
-        <v>-6.48348838451832</v>
-      </c>
-      <c r="H63" t="n">
-        <v>9517.27746008838</v>
-      </c>
-      <c r="I63" t="n">
-        <v>0.0000803359015911899</v>
-      </c>
-      <c r="J63" t="n">
-        <v>0.00675966731397236</v>
-      </c>
-      <c r="K63" t="n">
-        <v>5182.81281607738</v>
-      </c>
-      <c r="L63"/>
-      <c r="M63"/>
-      <c r="N63"/>
-      <c r="O63"/>
-      <c r="P63"/>
-      <c r="Q63"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>32</v>
-      </c>
-      <c r="B64" t="s">
-        <v>21</v>
-      </c>
-      <c r="C64" t="s">
-        <v>19</v>
-      </c>
-      <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" t="n">
-        <v>-6.42876217773409</v>
-      </c>
-      <c r="G64" t="n">
-        <v>-6.43896006791593</v>
-      </c>
-      <c r="H64" t="n">
-        <v>9450.95441963267</v>
-      </c>
-      <c r="I64" t="n">
-        <v>0.0000803511132607742</v>
-      </c>
-      <c r="J64" t="n">
-        <v>0.00676255786756616</v>
-      </c>
-      <c r="K64" t="n">
-        <v>5156.01109998202</v>
-      </c>
-      <c r="L64"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
-      <c r="P64"/>
-      <c r="Q64"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>32</v>
-      </c>
-      <c r="B65" t="s">
-        <v>21</v>
-      </c>
-      <c r="C65" t="s">
-        <v>20</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="n">
-        <v>-6.46738664429885</v>
-      </c>
-      <c r="G65" t="n">
-        <v>-6.48166369055342</v>
-      </c>
-      <c r="H65" t="n">
-        <v>9515.60063404187</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.0000803534404058461</v>
-      </c>
-      <c r="J65" t="n">
-        <v>0.00676289567888918</v>
-      </c>
-      <c r="K65" t="n">
-        <v>5200.12096009357</v>
-      </c>
-      <c r="L65"/>
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="O65"/>
-      <c r="P65"/>
-      <c r="Q65"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>32</v>
-      </c>
-      <c r="B66" t="s">
-        <v>22</v>
-      </c>
-      <c r="C66" t="s">
-        <v>19</v>
-      </c>
-      <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="n">
-        <v>1</v>
-      </c>
-      <c r="F66" t="n">
-        <v>-6.42879392055159</v>
-      </c>
-      <c r="G66" t="n">
-        <v>-6.43899181073343</v>
-      </c>
-      <c r="H66" t="n">
-        <v>9451.00098634594</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.0000803480888241652</v>
-      </c>
-      <c r="J66" t="n">
-        <v>0.00676209152823362</v>
-      </c>
-      <c r="K66" t="n">
-        <v>5188.44625830715</v>
-      </c>
-      <c r="L66"/>
-      <c r="M66"/>
-      <c r="N66"/>
-      <c r="O66"/>
-      <c r="P66"/>
-      <c r="Q66"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67" t="s">
-        <v>22</v>
-      </c>
-      <c r="C67" t="s">
-        <v>20</v>
-      </c>
-      <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" t="n">
-        <v>-6.47002620910434</v>
-      </c>
-      <c r="G67" t="n">
-        <v>-6.48430325535892</v>
-      </c>
-      <c r="H67" t="n">
-        <v>9519.47287561153</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.000080347911668574</v>
-      </c>
-      <c r="J67" t="n">
-        <v>0.00676206307276652</v>
-      </c>
-      <c r="K67" t="n">
-        <v>5196.92843629582</v>
-      </c>
-      <c r="L67"/>
-      <c r="M67"/>
-      <c r="N67"/>
-      <c r="O67"/>
-      <c r="P67"/>
-      <c r="Q67"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>33</v>
-      </c>
-      <c r="B68" t="s">
-        <v>18</v>
-      </c>
-      <c r="C68" t="s">
-        <v>19</v>
-      </c>
-      <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="n">
-        <v>1</v>
-      </c>
-      <c r="F68" t="n">
-        <v>-6.46105501407736</v>
-      </c>
-      <c r="G68" t="n">
-        <v>-6.46921332622283</v>
-      </c>
-      <c r="H68" t="n">
-        <v>9494.33594956889</v>
-      </c>
-      <c r="I68" t="n">
-        <v>0.0000749809738003076</v>
-      </c>
-      <c r="J68" t="n">
-        <v>0.00654778337064408</v>
-      </c>
-      <c r="K68" t="n">
-        <v>5223.83777701436</v>
-      </c>
-      <c r="L68"/>
-      <c r="M68"/>
-      <c r="N68"/>
-      <c r="O68"/>
-      <c r="P68"/>
-      <c r="Q68"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>33</v>
-      </c>
-      <c r="B69" t="s">
-        <v>18</v>
-      </c>
-      <c r="C69" t="s">
-        <v>20</v>
-      </c>
-      <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="n">
-        <v>1</v>
-      </c>
-      <c r="F69" t="n">
-        <v>-6.51710298192551</v>
-      </c>
-      <c r="G69" t="n">
-        <v>-6.52934045014372</v>
-      </c>
-      <c r="H69" t="n">
-        <v>9584.54244036084</v>
-      </c>
-      <c r="I69" t="n">
-        <v>0.0000749853401013443</v>
-      </c>
-      <c r="J69" t="n">
-        <v>0.00654991861742095</v>
-      </c>
-      <c r="K69" t="n">
-        <v>5225.20158469222</v>
-      </c>
-      <c r="L69"/>
-      <c r="M69"/>
-      <c r="N69"/>
-      <c r="O69"/>
-      <c r="P69"/>
-      <c r="Q69"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>33</v>
-      </c>
-      <c r="B70" t="s">
-        <v>21</v>
-      </c>
-      <c r="C70" t="s">
-        <v>19</v>
-      </c>
-      <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="n">
-        <v>1</v>
-      </c>
-      <c r="F70" t="n">
-        <v>-6.46720979550528</v>
-      </c>
-      <c r="G70" t="n">
-        <v>-6.47740768568712</v>
-      </c>
-      <c r="H70" t="n">
-        <v>9507.357074903</v>
-      </c>
-      <c r="I70" t="n">
-        <v>0.0000750090434852183</v>
-      </c>
-      <c r="J70" t="n">
-        <v>0.00655431788345669</v>
-      </c>
-      <c r="K70" t="n">
-        <v>5228.17585912406</v>
-      </c>
-      <c r="L70"/>
-      <c r="M70"/>
-      <c r="N70"/>
-      <c r="O70"/>
-      <c r="P70"/>
-      <c r="Q70"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>33</v>
-      </c>
-      <c r="B71" t="s">
-        <v>21</v>
-      </c>
-      <c r="C71" t="s">
-        <v>20</v>
-      </c>
-      <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="n">
-        <v>1</v>
-      </c>
-      <c r="F71" t="n">
-        <v>-6.5196466272262</v>
-      </c>
-      <c r="G71" t="n">
-        <v>-6.53392367348077</v>
-      </c>
-      <c r="H71" t="n">
-        <v>9592.26602899629</v>
-      </c>
-      <c r="I71" t="n">
-        <v>0.0000750206224158353</v>
-      </c>
-      <c r="J71" t="n">
-        <v>0.00655589262678087</v>
-      </c>
-      <c r="K71" t="n">
-        <v>5249.68246429117</v>
-      </c>
-      <c r="L71"/>
-      <c r="M71"/>
-      <c r="N71"/>
-      <c r="O71"/>
-      <c r="P71"/>
-      <c r="Q71"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>33</v>
-      </c>
-      <c r="B72" t="s">
-        <v>22</v>
-      </c>
-      <c r="C72" t="s">
-        <v>19</v>
-      </c>
-      <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="n">
-        <v>1</v>
-      </c>
-      <c r="F72" t="n">
-        <v>-6.46400431428354</v>
-      </c>
-      <c r="G72" t="n">
-        <v>-6.47420220446538</v>
-      </c>
-      <c r="H72" t="n">
-        <v>9502.65463395071</v>
-      </c>
-      <c r="I72" t="n">
-        <v>0.000075001729664675</v>
-      </c>
-      <c r="J72" t="n">
-        <v>0.0065531799888595</v>
-      </c>
-      <c r="K72" t="n">
-        <v>5239.7572907379</v>
-      </c>
-      <c r="L72"/>
-      <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="Q72"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>33</v>
-      </c>
-      <c r="B73" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" t="s">
-        <v>20</v>
-      </c>
-      <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="n">
-        <v>1</v>
-      </c>
-      <c r="F73" t="n">
-        <v>-6.51832153330266</v>
-      </c>
-      <c r="G73" t="n">
-        <v>-6.53259857955724</v>
-      </c>
-      <c r="H73" t="n">
-        <v>9590.32211621047</v>
-      </c>
-      <c r="I73" t="n">
-        <v>0.0000750063614617873</v>
-      </c>
-      <c r="J73" t="n">
-        <v>0.00655391108609953</v>
-      </c>
-      <c r="K73" t="n">
-        <v>5250.7919215142</v>
-      </c>
-      <c r="L73"/>
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
-      <c r="P73"/>
-      <c r="Q73"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
